--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4142A247-F422-BF4A-9056-4152F189FCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332E5D7F-7106-2640-BB37-7433DCF0DEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="176">
   <si>
     <t>Événement</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Triathlon de Joliette</t>
   </si>
   <si>
-    <t>info@triathlonjoliette.com</t>
-  </si>
-  <si>
     <t>Triathlon de Laval</t>
   </si>
   <si>
@@ -413,9 +410,6 @@
     <t>support@sportscapitale.com</t>
   </si>
   <si>
-    <t>Offrent entrainement sur leur site</t>
-  </si>
-  <si>
     <t>Tri-o-lac</t>
   </si>
   <si>
@@ -434,9 +428,6 @@
     <t>triathlon@boucherville.ca</t>
   </si>
   <si>
-    <t>Ils ont une section "Mon premier triathlon ou duathlon"</t>
-  </si>
-  <si>
     <t>epiqtriathlon@gmail.com</t>
   </si>
   <si>
@@ -467,9 +458,6 @@
     <t>Distances</t>
   </si>
   <si>
-    <t>Sprint Olynpique Initiation</t>
-  </si>
-  <si>
     <t>11-13 sept.</t>
   </si>
   <si>
@@ -494,18 +482,9 @@
     <t>Distance complète</t>
   </si>
   <si>
-    <t>Duathon Sprint</t>
-  </si>
-  <si>
-    <t>Duathlon Olympique</t>
-  </si>
-  <si>
     <t>Site</t>
   </si>
   <si>
-    <t>https://endurancedufjord.com/index.php/endurancefjord/index/triathlon_du_saguenay</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -573,6 +552,18 @@
   </si>
   <si>
     <t>J3T 1X4</t>
+  </si>
+  <si>
+    <t>Duathlon</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Olympique</t>
+  </si>
+  <si>
+    <t>Triathlon</t>
   </si>
 </sst>
 </file>
@@ -669,7 +660,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -682,6 +673,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1017,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1025,104 +1019,81 @@
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
     <col min="4" max="6" width="37.5" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -1133,16 +1104,16 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1170,16 +1141,16 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -1207,22 +1178,20 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1" t="s">
-        <v>135</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -1246,19 +1215,22 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
+      <c r="G6" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -1282,46 +1254,31 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G7" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>178</v>
-      </c>
+      <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -1331,124 +1288,128 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N10" s="1"/>
+        <v>149</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1462,39 +1423,37 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1509,28 +1468,40 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D12" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="F12" s="3"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
+      <c r="Q12" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1544,14 +1515,14 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1579,22 +1550,18 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C14" s="1"/>
       <c r="D14" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1618,38 +1585,32 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>157</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1663,30 +1624,38 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
+      <c r="Q16" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1700,37 +1669,30 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>170</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="E17" s="3"/>
       <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1744,30 +1706,37 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F18" s="3"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
+      <c r="Q18" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
@@ -1781,16 +1750,16 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1818,40 +1787,30 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -1865,17 +1824,19 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>168</v>
+        <v>66</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="D21" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -1884,25 +1845,21 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>156</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -1914,7 +1871,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>102</v>
@@ -1924,7 +1881,7 @@
         <v>121</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="1"/>
@@ -1933,23 +1890,25 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="S22" s="1"/>
+        <v>149</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -1961,38 +1920,40 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F23" s="4"/>
+      <c r="D23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="M23" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -2006,29 +1967,39 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="F24" s="4"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
+      <c r="Q24" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -2041,27 +2012,29 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -2076,55 +2049,55 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
-      <c r="Z26" s="5"/>
-      <c r="AA26" s="5"/>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2152,16 +2125,16 @@
     </row>
     <row r="28" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -2187,61 +2160,57 @@
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
+    <row r="29" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="5"/>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -2263,157 +2232,157 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-    </row>
-    <row r="32" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B32" s="5" t="s">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+    </row>
+    <row r="32" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9"/>
+    </row>
+    <row r="33" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="5"/>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5"/>
-      <c r="Z32" s="5"/>
-      <c r="AA32" s="5"/>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="5"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="2"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -2427,22 +2396,20 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -2466,23 +2433,23 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2501,29 +2468,31 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="2"/>
+      <c r="H37" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
@@ -2541,30 +2510,27 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="1"/>
+        <v>89</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="D38" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -2581,22 +2547,30 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="D39" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="1"/>
       <c r="H39" s="2"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
+      <c r="L39" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
@@ -2613,127 +2587,158 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F40" s="3"/>
-      <c r="L40" t="s">
-        <v>156</v>
-      </c>
-      <c r="M40" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>156</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E41" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="F41" s="3"/>
-      <c r="G41" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>129</v>
+      <c r="L41" t="s">
+        <v>149</v>
+      </c>
+      <c r="M41" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="5"/>
+      <c r="G42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>131</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" t="s">
-        <v>132</v>
-      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="L1:P1"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H36" r:id="rId1" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D34" r:id="rId2" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="D37" r:id="rId3" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D35" r:id="rId4" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D11" r:id="rId5" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
-    <hyperlink ref="D10" r:id="rId7" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
-    <hyperlink ref="G10" r:id="rId8" xr:uid="{390A6E3D-98D9-E348-8D55-B20902524152}"/>
-    <hyperlink ref="D14" r:id="rId9" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
-    <hyperlink ref="D15" r:id="rId10" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
-    <hyperlink ref="D16" r:id="rId11" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
-    <hyperlink ref="D17" r:id="rId12" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D20" r:id="rId13" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D21" r:id="rId15" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
-    <hyperlink ref="D25" r:id="rId16" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D29" r:id="rId17" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
-    <hyperlink ref="D33" r:id="rId18" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D38" r:id="rId19" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D40" r:id="rId20" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D41" r:id="rId21" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D43" r:id="rId22" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D44" r:id="rId23" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D6" r:id="rId24" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
-    <hyperlink ref="D5" r:id="rId25" xr:uid="{B351E82E-9F0E-664B-8FF4-A08DF588891D}"/>
-    <hyperlink ref="D12" r:id="rId26" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D13" r:id="rId27" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="G33" r:id="rId28" xr:uid="{DE922D89-8429-354F-B980-E4E2A7CE9396}"/>
-    <hyperlink ref="D31" r:id="rId29" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
+    <hyperlink ref="H37" r:id="rId1" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D35" r:id="rId2" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="D38" r:id="rId3" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D36" r:id="rId4" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D12" r:id="rId5" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
+    <hyperlink ref="D11" r:id="rId7" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
+    <hyperlink ref="D15" r:id="rId8" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
+    <hyperlink ref="D16" r:id="rId9" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
+    <hyperlink ref="D17" r:id="rId10" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D18" r:id="rId11" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D21" r:id="rId12" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D23" r:id="rId13" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
+    <hyperlink ref="D26" r:id="rId15" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D30" r:id="rId16" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
+    <hyperlink ref="D34" r:id="rId17" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D39" r:id="rId18" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D41" r:id="rId19" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D42" r:id="rId20" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D44" r:id="rId21" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D45" r:id="rId22" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D7" r:id="rId23" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="D6" r:id="rId24" xr:uid="{B351E82E-9F0E-664B-8FF4-A08DF588891D}"/>
+    <hyperlink ref="D13" r:id="rId25" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
+    <hyperlink ref="D14" r:id="rId26" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="D32" r:id="rId27" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332E5D7F-7106-2640-BB37-7433DCF0DEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F20409C-1629-6749-87C3-525FB0DD6F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="174">
   <si>
     <t>Événement</t>
   </si>
@@ -467,21 +467,6 @@
     <t>26-27 sept.</t>
   </si>
   <si>
-    <t>Initiation</t>
-  </si>
-  <si>
-    <t>Sprint</t>
-  </si>
-  <si>
-    <t>Olympique</t>
-  </si>
-  <si>
-    <t>Longue distance</t>
-  </si>
-  <si>
-    <t>Distance complète</t>
-  </si>
-  <si>
     <t>Site</t>
   </si>
   <si>
@@ -554,16 +539,25 @@
     <t>J3T 1X4</t>
   </si>
   <si>
-    <t>Duathlon</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Olympique</t>
-  </si>
-  <si>
-    <t>Triathlon</t>
+    <t>Triathlon Initiation</t>
+  </si>
+  <si>
+    <t>Triathlon Sprint</t>
+  </si>
+  <si>
+    <t>Triathlon Olympique</t>
+  </si>
+  <si>
+    <t>Triathlon demi distance</t>
+  </si>
+  <si>
+    <t>Triathlon Distance complète</t>
+  </si>
+  <si>
+    <t>Duathlon Sprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Duathlon Olympique</t>
   </si>
 </sst>
 </file>
@@ -660,7 +654,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -673,9 +667,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1011,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1023,77 +1014,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="L1" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12" t="s">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="R1" s="12"/>
+      <c r="R1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>162</v>
-      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -1104,16 +1119,16 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1141,16 +1156,16 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -1178,20 +1193,22 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -1215,22 +1232,19 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -1254,31 +1268,46 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
+      <c r="S7" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -1288,128 +1317,122 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-    </row>
-    <row r="9" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+    <row r="8" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>149</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
+      <c r="Q10" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1423,37 +1446,39 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="G11" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1471,37 +1496,25 @@
         <v>59</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C12" s="1"/>
       <c r="D12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>157</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1518,11 +1531,11 @@
         <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1550,18 +1563,22 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="D14" s="3" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1588,29 +1605,35 @@
         <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
+      <c r="Q15" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1624,38 +1647,30 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>150</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1669,30 +1684,37 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="3"/>
+        <v>118</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>158</v>
+      </c>
       <c r="F17" s="3"/>
-      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
+      <c r="Q17" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1706,37 +1728,30 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-      <c r="Q18" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
@@ -1750,16 +1765,16 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1787,30 +1802,40 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
+      <c r="Q20" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -1824,16 +1849,14 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>155</v>
@@ -1845,21 +1868,25 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -1871,17 +1898,17 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="1"/>
@@ -1890,25 +1917,23 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>149</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -1920,40 +1945,38 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F23" s="3"/>
+      <c r="D23" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="4"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -1970,36 +1993,30 @@
         <v>100</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>153</v>
-      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="M24" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -2012,29 +2029,27 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -2049,55 +2064,55 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
+    <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+      <c r="AA26" s="5"/>
     </row>
     <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2125,16 +2140,16 @@
     </row>
     <row r="28" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -2160,57 +2175,59 @@
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
     </row>
-    <row r="29" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
-      <c r="V29" s="5"/>
-      <c r="W29" s="5"/>
-      <c r="X29" s="5"/>
-      <c r="Y29" s="5"/>
-      <c r="Z29" s="5"/>
-      <c r="AA29" s="5"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -2232,157 +2249,155 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-    </row>
-    <row r="32" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-      <c r="AA32" s="9"/>
-    </row>
-    <row r="33" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+    <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
+    </row>
+    <row r="32" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
-      <c r="U33" s="5"/>
-      <c r="V33" s="5"/>
-      <c r="W33" s="5"/>
-      <c r="X33" s="5"/>
-      <c r="Y33" s="5"/>
-      <c r="Z33" s="5"/>
-      <c r="AA33" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
+      <c r="AA32" s="5"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -2396,20 +2411,22 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -2433,23 +2450,23 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2468,31 +2485,29 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="2" t="s">
-        <v>85</v>
-      </c>
+      <c r="H37" s="2"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
@@ -2510,27 +2525,30 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="C38" s="1"/>
       <c r="D38" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="M38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -2550,27 +2568,19 @@
         <v>82</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" s="3"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
       <c r="G39" s="1"/>
       <c r="H39" s="2"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
@@ -2590,155 +2600,119 @@
         <v>82</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="L40" t="s">
+        <v>144</v>
+      </c>
+      <c r="M40" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>156</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="L41" t="s">
-        <v>149</v>
-      </c>
-      <c r="M41" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>149</v>
+      <c r="G41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>128</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>127</v>
-      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="L1:P1"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H37" r:id="rId1" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D35" r:id="rId2" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="D38" r:id="rId3" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D36" r:id="rId4" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D12" r:id="rId5" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D8" r:id="rId6" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
-    <hyperlink ref="D11" r:id="rId7" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
-    <hyperlink ref="D15" r:id="rId8" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
-    <hyperlink ref="D16" r:id="rId9" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
-    <hyperlink ref="D17" r:id="rId10" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
-    <hyperlink ref="D18" r:id="rId11" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D21" r:id="rId12" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D23" r:id="rId13" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
-    <hyperlink ref="D26" r:id="rId15" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D30" r:id="rId16" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
-    <hyperlink ref="D34" r:id="rId17" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D39" r:id="rId18" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D41" r:id="rId19" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D42" r:id="rId20" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D44" r:id="rId21" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D45" r:id="rId22" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D7" r:id="rId23" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
-    <hyperlink ref="D6" r:id="rId24" xr:uid="{B351E82E-9F0E-664B-8FF4-A08DF588891D}"/>
-    <hyperlink ref="D13" r:id="rId25" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D14" r:id="rId26" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="D32" r:id="rId27" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
+    <hyperlink ref="H36" r:id="rId1" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D34" r:id="rId2" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="D37" r:id="rId3" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D35" r:id="rId4" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D11" r:id="rId5" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
+    <hyperlink ref="D10" r:id="rId7" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
+    <hyperlink ref="D14" r:id="rId8" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
+    <hyperlink ref="D15" r:id="rId9" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
+    <hyperlink ref="D16" r:id="rId10" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D17" r:id="rId11" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D20" r:id="rId12" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D22" r:id="rId13" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D21" r:id="rId14" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
+    <hyperlink ref="D25" r:id="rId15" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D29" r:id="rId16" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
+    <hyperlink ref="D33" r:id="rId17" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D38" r:id="rId18" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D40" r:id="rId19" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D41" r:id="rId20" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D43" r:id="rId21" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D44" r:id="rId22" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D6" r:id="rId23" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="D5" r:id="rId24" xr:uid="{B351E82E-9F0E-664B-8FF4-A08DF588891D}"/>
+    <hyperlink ref="D12" r:id="rId25" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
+    <hyperlink ref="D13" r:id="rId26" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="D31" r:id="rId27" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F20409C-1629-6749-87C3-525FB0DD6F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB07845-6ABA-B64D-9C81-9318D3227D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -551,13 +551,13 @@
     <t>Triathlon demi distance</t>
   </si>
   <si>
-    <t>Triathlon Distance complète</t>
-  </si>
-  <si>
     <t>Duathlon Sprint</t>
   </si>
   <si>
     <t xml:space="preserve"> Duathlon Olympique</t>
+  </si>
+  <si>
+    <t>Triathlon longue distance</t>
   </si>
 </sst>
 </file>
@@ -1058,13 +1058,13 @@
         <v>170</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>154</v>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB07845-6ABA-B64D-9C81-9318D3227D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CDFA73-3049-9948-B9CB-2495ACFE9F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="176">
   <si>
     <t>Événement</t>
   </si>
@@ -558,6 +558,12 @@
   </si>
   <si>
     <t>Triathlon longue distance</t>
+  </si>
+  <si>
+    <t>31 octobre</t>
+  </si>
+  <si>
+    <t>TEST</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -2683,6 +2689,14 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>175</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CDFA73-3049-9948-B9CB-2495ACFE9F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C010FFB-198C-F241-9641-CE79D5ACE65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -533,12 +533,6 @@
     <t>TQ</t>
   </si>
   <si>
-    <t>Code Postal</t>
-  </si>
-  <si>
-    <t>J3T 1X4</t>
-  </si>
-  <si>
     <t>Triathlon Initiation</t>
   </si>
   <si>
@@ -564,6 +558,12 @@
   </si>
   <si>
     <t>TEST</t>
+  </si>
+  <si>
+    <t>350 Rue Marguerite d'Youville, Nicolet, QC J3T 1X4</t>
+  </si>
+  <si>
+    <t>Lieu</t>
   </si>
 </sst>
 </file>
@@ -1017,6 +1017,7 @@
     <col min="4" max="6" width="37.5" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="16" max="16" width="13.6640625" customWidth="1"/>
+    <col min="18" max="18" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
@@ -1048,29 +1049,29 @@
         <v>139</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>154</v>
@@ -1295,7 +1296,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
@@ -2692,10 +2693,10 @@
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C010FFB-198C-F241-9641-CE79D5ACE65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6236658-5273-2F43-8C42-74201432E875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -179,9 +179,6 @@
     <t>Chaudière-Appalaches</t>
   </si>
   <si>
-    <t>Contact / Site Officiel</t>
-  </si>
-  <si>
     <t>14 fév.</t>
   </si>
   <si>
@@ -564,6 +561,9 @@
   </si>
   <si>
     <t>Lieu</t>
+  </si>
+  <si>
+    <t>Contact</t>
   </si>
 </sst>
 </file>
@@ -1031,53 +1031,53 @@
         <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1089,13 +1089,13 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>18</v>
@@ -1126,13 +1126,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>20</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>25</v>
@@ -1209,12 +1209,12 @@
         <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -1248,7 +1248,7 @@
         <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
@@ -1284,36 +1284,36 @@
         <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1326,16 +1326,16 @@
     </row>
     <row r="8" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -1363,19 +1363,19 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1384,13 +1384,13 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>2</v>
@@ -1417,10 +1417,10 @@
         <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -1429,16 +1429,16 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -1462,30 +1462,30 @@
         <v>32</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1500,14 +1500,14 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1535,14 +1535,14 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>4</v>
@@ -1579,12 +1579,12 @@
         <v>28</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1609,19 +1609,19 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
@@ -1630,16 +1630,16 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>33</v>
@@ -1663,7 +1663,7 @@
         <v>24</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
@@ -1700,10 +1700,10 @@
         <v>34</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F17" s="3"/>
       <c r="H17" s="1"/>
@@ -1711,16 +1711,16 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
@@ -1772,13 +1772,13 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>9</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -1818,10 +1818,10 @@
         <v>36</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
@@ -1830,18 +1830,18 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -1856,17 +1856,17 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -1875,24 +1875,24 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
@@ -1905,17 +1905,17 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="1"/>
@@ -1924,21 +1924,21 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -1952,17 +1952,17 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="1"/>
@@ -1972,18 +1972,18 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="4"/>
@@ -2012,13 +2012,13 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>10</v>
@@ -2073,16 +2073,16 @@
     </row>
     <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2110,16 +2110,16 @@
     </row>
     <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2147,16 +2147,16 @@
     </row>
     <row r="28" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -2184,14 +2184,14 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
@@ -2233,7 +2233,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2258,15 +2258,15 @@
     </row>
     <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
@@ -2275,21 +2275,21 @@
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
       <c r="T31" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U31" s="9"/>
       <c r="V31" s="9"/>
@@ -2301,7 +2301,7 @@
     </row>
     <row r="32" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>39</v>
@@ -2338,14 +2338,14 @@
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -2355,18 +2355,18 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>42</v>
@@ -2390,7 +2390,7 @@
         <v>22</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2418,21 +2418,21 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>13</v>
@@ -2472,7 +2472,7 @@
       <c r="F36" s="4"/>
       <c r="G36" s="1"/>
       <c r="H36" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -2495,19 +2495,19 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -2532,17 +2532,17 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="1"/>
@@ -2551,10 +2551,10 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="8"/>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>43</v>
@@ -2616,22 +2616,22 @@
         <v>44</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F40" s="3"/>
       <c r="L40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>45</v>
@@ -2640,23 +2640,23 @@
         <v>46</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="3"/>
@@ -2667,36 +2667,36 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6236658-5273-2F43-8C42-74201432E875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F12DB9-BA97-3643-AAF3-88F657654DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -2701,33 +2701,33 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H36" r:id="rId1" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D34" r:id="rId2" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="D37" r:id="rId3" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D35" r:id="rId4" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D11" r:id="rId5" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
-    <hyperlink ref="D10" r:id="rId7" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
-    <hyperlink ref="D14" r:id="rId8" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
-    <hyperlink ref="D15" r:id="rId9" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
-    <hyperlink ref="D16" r:id="rId10" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
-    <hyperlink ref="D17" r:id="rId11" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D20" r:id="rId12" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D22" r:id="rId13" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D21" r:id="rId14" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
-    <hyperlink ref="D25" r:id="rId15" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D29" r:id="rId16" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
-    <hyperlink ref="D33" r:id="rId17" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D38" r:id="rId18" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D40" r:id="rId19" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D41" r:id="rId20" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D43" r:id="rId21" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D44" r:id="rId22" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D6" r:id="rId23" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
-    <hyperlink ref="D5" r:id="rId24" xr:uid="{B351E82E-9F0E-664B-8FF4-A08DF588891D}"/>
-    <hyperlink ref="D12" r:id="rId25" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D13" r:id="rId26" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="D31" r:id="rId27" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
+    <hyperlink ref="D31" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
+    <hyperlink ref="D13" r:id="rId3" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="D12" r:id="rId4" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
+    <hyperlink ref="D44" r:id="rId5" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D43" r:id="rId6" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D41" r:id="rId7" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D40" r:id="rId8" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D38" r:id="rId9" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D33" r:id="rId10" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D29" r:id="rId11" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
+    <hyperlink ref="D25" r:id="rId12" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D21" r:id="rId13" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D20" r:id="rId15" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D16" r:id="rId17" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D15" r:id="rId18" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
+    <hyperlink ref="D14" r:id="rId19" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
+    <hyperlink ref="D10" r:id="rId20" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
+    <hyperlink ref="D11" r:id="rId21" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
+    <hyperlink ref="D35" r:id="rId22" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D37" r:id="rId23" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D34" r:id="rId24" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H36" r:id="rId25" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D5" r:id="rId26" xr:uid="{B351E82E-9F0E-664B-8FF4-A08DF588891D}"/>
+    <hyperlink ref="D6" r:id="rId27" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F12DB9-BA97-3643-AAF3-88F657654DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F307FAD-77ED-E94C-A92E-31BD721791C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="181">
   <si>
     <t>Événement</t>
   </si>
@@ -101,21 +101,12 @@
     <t>info@pentathlondesneiges.com</t>
   </si>
   <si>
-    <t>Aquathlon ETA 2</t>
-  </si>
-  <si>
     <t>Montréal</t>
   </si>
   <si>
-    <t>info@triathloneta.com</t>
-  </si>
-  <si>
     <t>Estrie</t>
   </si>
   <si>
-    <t>Aquathlon de Sherbrooke</t>
-  </si>
-  <si>
     <t>Aquathlon des Remparts</t>
   </si>
   <si>
@@ -188,9 +179,6 @@
     <t>14-22 fév.</t>
   </si>
   <si>
-    <t>22 fév.</t>
-  </si>
-  <si>
     <t>2 mai</t>
   </si>
   <si>
@@ -431,9 +419,6 @@
     <t>info@opustriathlon.com</t>
   </si>
   <si>
-    <t>Sherbrooke</t>
-  </si>
-  <si>
     <t>Triathlon de la Vallée-du-Richelieu Rouville</t>
   </si>
   <si>
@@ -564,6 +549,36 @@
   </si>
   <si>
     <t>Contact</t>
+  </si>
+  <si>
+    <t>Opus Triathlon</t>
+  </si>
+  <si>
+    <t>2300 De la Terrasse St, Québec City, Quebec G1V 0A6</t>
+  </si>
+  <si>
+    <t>https://www.opustriathlon.com/aquathlon-de-quebec</t>
+  </si>
+  <si>
+    <t>https://www.pentathlondesneiges.com</t>
+  </si>
+  <si>
+    <t>GROUPE PENTATHLON</t>
+  </si>
+  <si>
+    <t>255 Grande Allée O, Québec, QC G1R 2H1</t>
+  </si>
+  <si>
+    <t>2500, boulevard de l'Université, Sherbrooke, QC, J1K 2R1</t>
+  </si>
+  <si>
+    <t>Aquathlon S-Triman</t>
+  </si>
+  <si>
+    <t>https://www.triathlonsherbrooke.com/aquathlon-2026</t>
+  </si>
+  <si>
+    <t>Club de Triathlon de Sherbrooke</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1031,53 +1046,53 @@
         <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1089,23 +1104,31 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="E2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1115,7 +1138,9 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -1126,23 +1151,31 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1163,23 +1196,31 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="D4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>180</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1189,7 +1230,9 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="T4" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -1200,22 +1243,19 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -1239,31 +1279,46 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
+      <c r="S6" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1273,128 +1328,122 @@
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-    </row>
-    <row r="8" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>143</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1408,37 +1457,39 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1453,40 +1504,28 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>151</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="1" t="s">
-        <v>96</v>
-      </c>
+      <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1500,14 +1539,14 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1535,18 +1574,22 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="D13" s="3" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1570,32 +1613,38 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="F14" s="3"/>
-      <c r="G14" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -1609,38 +1658,30 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>144</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1654,30 +1695,37 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" s="3"/>
+        <v>113</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
+      <c r="Q16" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1691,37 +1739,30 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1735,16 +1776,16 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1772,30 +1813,40 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -1809,16 +1860,14 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C20" s="1"/>
       <c r="D20" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>149</v>
@@ -1830,21 +1879,25 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
+        <v>138</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -1856,17 +1909,17 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -1875,25 +1928,23 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>143</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -1905,40 +1956,38 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F22" s="3"/>
+      <c r="D22" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="4"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -1952,39 +2001,33 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>147</v>
-      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="M23" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -1997,29 +2040,27 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -2034,52 +2075,52 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
+    <row r="25" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5"/>
+      <c r="AA25" s="5"/>
     </row>
     <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>69</v>
@@ -2116,10 +2157,10 @@
         <v>71</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2145,57 +2186,59 @@
       <c r="Z27" s="5"/>
       <c r="AA27" s="5"/>
     </row>
-    <row r="28" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
-      <c r="X28" s="5"/>
-      <c r="Y28" s="5"/>
-      <c r="Z28" s="5"/>
-      <c r="AA28" s="5"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>119</v>
+      </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -2217,157 +2260,155 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="1" t="s">
+    <row r="30" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
+    </row>
+    <row r="31" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="D31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-    </row>
-    <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-    </row>
-    <row r="32" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="5"/>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5"/>
-      <c r="Z32" s="5"/>
-      <c r="AA32" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+      <c r="AA31" s="5"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2381,20 +2422,22 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -2418,23 +2461,23 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H35" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2453,31 +2496,29 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="H36" s="2"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
@@ -2495,27 +2536,30 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C37" s="1"/>
       <c r="D37" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>121</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="1"/>
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="M37" s="1"/>
+      <c r="L37" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -2532,30 +2576,22 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F38" s="3"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -2572,162 +2608,131 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="L39" t="s">
+        <v>138</v>
+      </c>
+      <c r="M39" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>150</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="L40" t="s">
-        <v>143</v>
-      </c>
-      <c r="M40" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>143</v>
+      <c r="G40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>127</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>126</v>
-      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
-    <hyperlink ref="D31" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
-    <hyperlink ref="D13" r:id="rId3" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="D12" r:id="rId4" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D44" r:id="rId5" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D43" r:id="rId6" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D41" r:id="rId7" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D40" r:id="rId8" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D38" r:id="rId9" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D33" r:id="rId10" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D29" r:id="rId11" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
-    <hyperlink ref="D25" r:id="rId12" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D21" r:id="rId13" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D20" r:id="rId15" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D16" r:id="rId17" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
-    <hyperlink ref="D15" r:id="rId18" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
-    <hyperlink ref="D14" r:id="rId19" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
-    <hyperlink ref="D10" r:id="rId20" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
-    <hyperlink ref="D11" r:id="rId21" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D35" r:id="rId22" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D37" r:id="rId23" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D34" r:id="rId24" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H36" r:id="rId25" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D5" r:id="rId26" xr:uid="{B351E82E-9F0E-664B-8FF4-A08DF588891D}"/>
-    <hyperlink ref="D6" r:id="rId27" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="D6" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
+    <hyperlink ref="D30" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
+    <hyperlink ref="D12" r:id="rId3" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="D11" r:id="rId4" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
+    <hyperlink ref="D43" r:id="rId5" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D42" r:id="rId6" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D40" r:id="rId7" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D39" r:id="rId8" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D37" r:id="rId9" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D32" r:id="rId10" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D28" r:id="rId11" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
+    <hyperlink ref="D24" r:id="rId12" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D20" r:id="rId13" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
+    <hyperlink ref="D21" r:id="rId14" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D19" r:id="rId15" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D16" r:id="rId16" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D15" r:id="rId17" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D14" r:id="rId18" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
+    <hyperlink ref="D13" r:id="rId19" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
+    <hyperlink ref="D9" r:id="rId20" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
+    <hyperlink ref="D10" r:id="rId21" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
+    <hyperlink ref="D34" r:id="rId22" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D36" r:id="rId23" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D33" r:id="rId24" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H35" r:id="rId25" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D5" r:id="rId26" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="E2" r:id="rId27" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
+    <hyperlink ref="D4" r:id="rId28" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F307FAD-77ED-E94C-A92E-31BD721791C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BD49A1-0251-F14D-8A9C-FE53309F2D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="187">
   <si>
     <t>Événement</t>
   </si>
@@ -554,9 +554,6 @@
     <t>Opus Triathlon</t>
   </si>
   <si>
-    <t>2300 De la Terrasse St, Québec City, Quebec G1V 0A6</t>
-  </si>
-  <si>
     <t>https://www.opustriathlon.com/aquathlon-de-quebec</t>
   </si>
   <si>
@@ -579,6 +576,27 @@
   </si>
   <si>
     <t>Club de Triathlon de Sherbrooke</t>
+  </si>
+  <si>
+    <t>4 avril</t>
+  </si>
+  <si>
+    <t>Aquathlon de Montréal</t>
+  </si>
+  <si>
+    <t>2100 Boulevard Édouard-Montpetit, Montréal, QC, H3T 1J4</t>
+  </si>
+  <si>
+    <t>triudem@gmail.com</t>
+  </si>
+  <si>
+    <t>triathlonudem.com/</t>
+  </si>
+  <si>
+    <t>Club de Triathlon de l’Université de Montréal</t>
+  </si>
+  <si>
+    <t>2300 De la Terrasse St, Québec, Quebec G1V 0A6</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1116,7 +1134,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>158</v>
@@ -1127,7 +1145,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1163,18 +1181,18 @@
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1199,7 +1217,7 @@
         <v>131</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
@@ -1208,18 +1226,18 @@
         <v>112</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>158</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1243,22 +1261,31 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="J5" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1268,7 +1295,9 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
+      <c r="T5" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
@@ -1279,46 +1308,31 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G6" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>168</v>
-      </c>
+      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1328,106 +1342,112 @@
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
-    <row r="7" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1438,12 +1458,12 @@
       <c r="M9" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="N9" s="1"/>
+      <c r="N9" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1457,24 +1477,22 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G10" s="3"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1507,25 +1525,37 @@
         <v>54</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D11" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" s="3"/>
+        <v>93</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
+      <c r="Q11" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1542,11 +1572,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1574,22 +1604,18 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C13" s="1"/>
       <c r="D13" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1616,35 +1642,29 @@
         <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>139</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -1658,30 +1678,38 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
+      <c r="Q15" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1695,37 +1723,30 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>152</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E16" s="3"/>
       <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1739,30 +1760,37 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17" s="3"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
+      <c r="Q17" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1776,16 +1804,16 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1813,40 +1841,30 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -1860,17 +1878,19 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="D20" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
@@ -1892,12 +1912,8 @@
       <c r="Q20" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="R20" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -1909,17 +1925,17 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -1944,7 +1960,9 @@
       <c r="R21" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="S21" s="1"/>
+      <c r="S21" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -1956,25 +1974,27 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F22" s="4"/>
+      <c r="D22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="M22" s="1" t="s">
         <v>138</v>
       </c>
@@ -2004,20 +2024,22 @@
         <v>95</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
         <v>138</v>
       </c>
@@ -2026,8 +2048,12 @@
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
+      <c r="Q23" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -2040,27 +2066,29 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+        <v>132</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -2075,55 +2103,55 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2151,16 +2179,16 @@
     </row>
     <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2186,59 +2214,57 @@
       <c r="Z27" s="5"/>
       <c r="AA27" s="5"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+    <row r="28" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="5"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="5"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -2260,155 +2286,157 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+    </row>
+    <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E31" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-    </row>
-    <row r="31" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
+    </row>
+    <row r="32" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
-      <c r="V31" s="5"/>
-      <c r="W31" s="5"/>
-      <c r="X31" s="5"/>
-      <c r="Y31" s="5"/>
-      <c r="Z31" s="5"/>
-      <c r="AA31" s="5"/>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
+      <c r="AA32" s="5"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
+        <v>101</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="2"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
+      <c r="Q33" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2422,22 +2450,20 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -2461,23 +2487,23 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2" t="s">
-        <v>80</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2496,29 +2522,31 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F36" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="2"/>
+      <c r="H36" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
@@ -2536,30 +2564,27 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="D37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -2579,19 +2604,27 @@
         <v>77</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="D38" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -2611,128 +2644,162 @@
         <v>77</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="L39" t="s">
-        <v>138</v>
-      </c>
-      <c r="M39" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>138</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="F40" s="3"/>
-      <c r="G40" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>122</v>
+      <c r="L40" t="s">
+        <v>138</v>
+      </c>
+      <c r="M40" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="5"/>
+      <c r="G41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>124</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>167</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D6" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
-    <hyperlink ref="D30" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
-    <hyperlink ref="D12" r:id="rId3" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="D11" r:id="rId4" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D43" r:id="rId5" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D42" r:id="rId6" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D40" r:id="rId7" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D39" r:id="rId8" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D37" r:id="rId9" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D32" r:id="rId10" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D28" r:id="rId11" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
-    <hyperlink ref="D24" r:id="rId12" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D20" r:id="rId13" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
-    <hyperlink ref="D21" r:id="rId14" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D19" r:id="rId15" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D16" r:id="rId16" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D15" r:id="rId17" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
-    <hyperlink ref="D14" r:id="rId18" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
-    <hyperlink ref="D13" r:id="rId19" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
-    <hyperlink ref="D9" r:id="rId20" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
-    <hyperlink ref="D10" r:id="rId21" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D34" r:id="rId22" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D36" r:id="rId23" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D33" r:id="rId24" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H35" r:id="rId25" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D5" r:id="rId26" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
+    <hyperlink ref="D31" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
+    <hyperlink ref="D13" r:id="rId3" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="D12" r:id="rId4" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
+    <hyperlink ref="D44" r:id="rId5" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D43" r:id="rId6" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D41" r:id="rId7" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D40" r:id="rId8" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D38" r:id="rId9" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D33" r:id="rId10" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D29" r:id="rId11" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
+    <hyperlink ref="D25" r:id="rId12" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D21" r:id="rId13" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D20" r:id="rId15" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D16" r:id="rId17" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D15" r:id="rId18" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
+    <hyperlink ref="D14" r:id="rId19" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
+    <hyperlink ref="D10" r:id="rId20" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
+    <hyperlink ref="D11" r:id="rId21" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
+    <hyperlink ref="D35" r:id="rId22" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D37" r:id="rId23" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D34" r:id="rId24" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H36" r:id="rId25" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D6" r:id="rId26" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
     <hyperlink ref="E2" r:id="rId27" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
     <hyperlink ref="D4" r:id="rId28" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
+    <hyperlink ref="J5" r:id="rId29" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
+    <hyperlink ref="D5" r:id="rId30" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BD49A1-0251-F14D-8A9C-FE53309F2D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C765501-39EF-5945-B160-ED85D6F54C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="189">
   <si>
     <t>Événement</t>
   </si>
@@ -597,6 +597,12 @@
   </si>
   <si>
     <t>2300 De la Terrasse St, Québec, Quebec G1V 0A6</t>
+  </si>
+  <si>
+    <t>Les Remparts du Collège Militaire Royal de Saint-Jean</t>
+  </si>
+  <si>
+    <t>15 Rue Jacques-Cartier N,, Saint-Jean-sur-Richelieu, QC, J3B 8R8</t>
   </si>
 </sst>
 </file>
@@ -1320,10 +1326,17 @@
         <v>126</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1333,7 +1346,9 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
+      <c r="T6" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C765501-39EF-5945-B160-ED85D6F54C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E95D8D-C9BB-7D4A-91A4-FE5F47CEDD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="196">
   <si>
     <t>Événement</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Triathlon de Joliette</t>
   </si>
   <si>
+    <t>info@triathlonjoliette.com</t>
+  </si>
+  <si>
     <t>Triathlon de Laval</t>
   </si>
   <si>
@@ -119,9 +122,6 @@
     <t>Triathlon de Québec</t>
   </si>
   <si>
-    <t>info@triathlondequebec.com</t>
-  </si>
-  <si>
     <t>Lanaudière</t>
   </si>
   <si>
@@ -185,15 +185,6 @@
     <t>16-17 mai</t>
   </si>
   <si>
-    <t>24 mai</t>
-  </si>
-  <si>
-    <t>Duathlon St-Eustache</t>
-  </si>
-  <si>
-    <t>info@duathlonsteustache.com</t>
-  </si>
-  <si>
     <t>30 mai</t>
   </si>
   <si>
@@ -314,9 +305,6 @@
     <t>bionicktriathlon.info@gmail.com</t>
   </si>
   <si>
-    <t>Triathlon laval</t>
-  </si>
-  <si>
     <t>info@triathlonlaval.org</t>
   </si>
   <si>
@@ -362,9 +350,6 @@
     <t>trinicolet@gmail.com</t>
   </si>
   <si>
-    <t>admin@triathlonjoliette.com</t>
-  </si>
-  <si>
     <t>Triomax</t>
   </si>
   <si>
@@ -425,9 +410,6 @@
     <t>info@trivdr.com</t>
   </si>
   <si>
-    <t>info@coursesnature.com</t>
-  </si>
-  <si>
     <t>Triathlon du parc national de la Yamaska</t>
   </si>
   <si>
@@ -603,6 +585,45 @@
   </si>
   <si>
     <t>15 Rue Jacques-Cartier N,, Saint-Jean-sur-Richelieu, QC, J3B 8R8</t>
+  </si>
+  <si>
+    <t>Club les Zéclairs de Nicolet</t>
+  </si>
+  <si>
+    <t>3137 Rue Laberge, Québec, QC, G1X 4B5</t>
+  </si>
+  <si>
+    <t>triathlondequebec@gmail.com</t>
+  </si>
+  <si>
+    <t>20 St-Charles Borromée sud, Joliette, QC, J6E 4T1</t>
+  </si>
+  <si>
+    <t>Club Jet Triathlon</t>
+  </si>
+  <si>
+    <t>901 Avenue du Parc, Laval, QC, H7E 2T7</t>
+  </si>
+  <si>
+    <t>Triathlon Laval</t>
+  </si>
+  <si>
+    <t>1925 Chem. Rouville, Saint-Jean-Baptiste, QC J0L 2B0</t>
+  </si>
+  <si>
+    <t>Triathlon Élite Développement</t>
+  </si>
+  <si>
+    <t>https://trivdr.triathlondeverdun.com</t>
+  </si>
+  <si>
+    <t>https://www.coursesnature.com/evenements/triathlon-du-parc-national-de-la-yamaska</t>
+  </si>
+  <si>
+    <t>info@marathonmontmegantic.com</t>
+  </si>
+  <si>
+    <t>Chem. Roxton S, Roxton Pond, QC J0E 1Z0</t>
   </si>
 </sst>
 </file>
@@ -1047,11 +1068,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
     <col min="4" max="6" width="37.5" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
@@ -1061,62 +1082,62 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1131,27 +1152,27 @@
         <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1163,7 +1184,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1178,27 +1199,27 @@
         <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1220,30 +1241,30 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1255,7 +1276,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1267,30 +1288,30 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1302,7 +1323,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1317,25 +1338,25 @@
         <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1347,7 +1368,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1365,39 +1386,41 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1408,77 +1431,97 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="J9" s="2" t="s">
+        <v>186</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>138</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1492,37 +1535,43 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="J10" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1537,39 +1586,45 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>192</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>92</v>
+        <v>191</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+      <c r="J11" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N11" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1584,27 +1639,41 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>124</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="D12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E12" s="3"/>
+        <v>194</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -1619,18 +1688,22 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D13" s="3" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1654,32 +1727,38 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" s="3"/>
+        <v>106</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="F14" s="3"/>
-      <c r="G14" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -1693,38 +1772,30 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>139</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1738,30 +1809,37 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
+      <c r="Q16" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1775,37 +1853,30 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1819,16 +1890,16 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1856,30 +1927,40 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -1893,19 +1974,17 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C20" s="1"/>
       <c r="D20" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
@@ -1914,21 +1993,25 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -1940,17 +2023,17 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -1959,25 +2042,23 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>138</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -1989,40 +2070,38 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F22" s="3"/>
+      <c r="D22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" s="4"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -2036,39 +2115,33 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>142</v>
-      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="M23" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -2081,29 +2154,27 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -2118,42 +2189,42 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5"/>
+      <c r="AA25" s="5"/>
     </row>
     <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
@@ -2163,10 +2234,10 @@
         <v>64</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2194,13 +2265,13 @@
     </row>
     <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>69</v>
@@ -2229,57 +2300,59 @@
       <c r="Z27" s="5"/>
       <c r="AA27" s="5"/>
     </row>
-    <row r="28" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
-      <c r="X28" s="5"/>
-      <c r="Y28" s="5"/>
-      <c r="Z28" s="5"/>
-      <c r="AA28" s="5"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -2301,157 +2374,155 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-    </row>
-    <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-    </row>
-    <row r="32" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="5" t="s">
+    <row r="30" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
+    </row>
+    <row r="31" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="5"/>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5"/>
-      <c r="Z32" s="5"/>
-      <c r="AA32" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+      <c r="AA31" s="5"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2465,20 +2536,22 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -2502,23 +2575,23 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H35" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2537,31 +2610,29 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="H36" s="2"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
@@ -2579,27 +2650,30 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>68</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C37" s="1"/>
       <c r="D37" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="1"/>
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="M37" s="1"/>
+      <c r="L37" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -2616,30 +2690,22 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F38" s="3"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -2656,165 +2722,138 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="L39" t="s">
+        <v>132</v>
+      </c>
+      <c r="M39" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>145</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="L40" t="s">
-        <v>138</v>
-      </c>
-      <c r="M40" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>138</v>
+      <c r="G40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>123</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>122</v>
-      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
-    <hyperlink ref="D31" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
-    <hyperlink ref="D13" r:id="rId3" display="mailto:info@coursesnature.com" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="D12" r:id="rId4" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D44" r:id="rId5" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D43" r:id="rId6" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D41" r:id="rId7" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D40" r:id="rId8" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D38" r:id="rId9" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D33" r:id="rId10" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D29" r:id="rId11" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
-    <hyperlink ref="D25" r:id="rId12" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D21" r:id="rId13" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D20" r:id="rId15" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D16" r:id="rId17" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
-    <hyperlink ref="D15" r:id="rId18" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
-    <hyperlink ref="D14" r:id="rId19" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
-    <hyperlink ref="D10" r:id="rId20" xr:uid="{749AC3C7-F098-B74E-AEDF-D3CBE1F14AB7}"/>
-    <hyperlink ref="D11" r:id="rId21" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D35" r:id="rId22" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D37" r:id="rId23" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D34" r:id="rId24" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H36" r:id="rId25" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D6" r:id="rId26" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
-    <hyperlink ref="E2" r:id="rId27" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
-    <hyperlink ref="D4" r:id="rId28" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
-    <hyperlink ref="J5" r:id="rId29" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
-    <hyperlink ref="D5" r:id="rId30" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
+    <hyperlink ref="D30" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
+    <hyperlink ref="D11" r:id="rId3" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
+    <hyperlink ref="D43" r:id="rId4" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D42" r:id="rId5" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D40" r:id="rId6" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D39" r:id="rId7" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D37" r:id="rId8" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D32" r:id="rId9" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D28" r:id="rId10" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
+    <hyperlink ref="D24" r:id="rId11" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D20" r:id="rId12" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
+    <hyperlink ref="D21" r:id="rId13" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D19" r:id="rId14" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D16" r:id="rId15" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D15" r:id="rId16" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D14" r:id="rId17" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
+    <hyperlink ref="D13" r:id="rId18" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
+    <hyperlink ref="D10" r:id="rId19" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
+    <hyperlink ref="D34" r:id="rId20" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D36" r:id="rId21" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D33" r:id="rId22" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H35" r:id="rId23" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D6" r:id="rId24" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="E2" r:id="rId25" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
+    <hyperlink ref="D4" r:id="rId26" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
+    <hyperlink ref="J5" r:id="rId27" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
+    <hyperlink ref="D5" r:id="rId28" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
+    <hyperlink ref="D8" r:id="rId29" display="mailto:triathlondequebec@gmail.com" xr:uid="{73850B34-F1B7-FA48-A070-95C1FFA6FD13}"/>
+    <hyperlink ref="J9" r:id="rId30" display="https://www.google.com/maps/search/?q=Cegep%20R%C3%A9gional%20de%20Lanaudi%C3%A8re%2020%20St-Charles%20Borrom%C3%A9e%20sud%20Joliette%2C%20QC%20J6E%204T1" xr:uid="{B1ADDF14-CFF1-A64F-B451-75A4B753FEB1}"/>
+    <hyperlink ref="J10" r:id="rId31" display="https://www.google.com/maps/search/?q=Centre%20de%20la%20Nature%20%20901%20Avenue%20du%20Parc%20Laval%2C%20QC%20H7E%202T7" xr:uid="{26BECA49-1FB0-6E48-AEA5-586D56437FCE}"/>
+    <hyperlink ref="J11" r:id="rId32" display="https://www.google.com/maps/search/?q=Domaine%20international%20de%20Rouville%201925%20Chem.%20Rouville%2C%20Saint-Jean-Baptiste%2C%20QC%20J0L%202B0%20Saint-Jean-Baptiste%2C%20QC%20" xr:uid="{23DC6288-A0CC-9543-AE7F-D801B3F5045D}"/>
+    <hyperlink ref="E11" r:id="rId33" xr:uid="{44C69AEF-33F5-5D43-97CF-FD06227199DB}"/>
+    <hyperlink ref="E12" r:id="rId34" xr:uid="{B9A33CB1-2829-2647-947B-C4DAF8119C7B}"/>
+    <hyperlink ref="D12" r:id="rId35" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E95D8D-C9BB-7D4A-91A4-FE5F47CEDD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB1DCF3-6346-C44B-900A-2C1DD710F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="203">
   <si>
     <t>Événement</t>
   </si>
@@ -197,9 +197,6 @@
     <t>13 juin</t>
   </si>
   <si>
-    <t>Tri/Duathlon St-Lambert</t>
-  </si>
-  <si>
     <t>14 juin</t>
   </si>
   <si>
@@ -350,9 +347,6 @@
     <t>trinicolet@gmail.com</t>
   </si>
   <si>
-    <t>Triomax</t>
-  </si>
-  <si>
     <t>info@triathlon.qc.ca</t>
   </si>
   <si>
@@ -584,9 +578,6 @@
     <t>Les Remparts du Collège Militaire Royal de Saint-Jean</t>
   </si>
   <si>
-    <t>15 Rue Jacques-Cartier N,, Saint-Jean-sur-Richelieu, QC, J3B 8R8</t>
-  </si>
-  <si>
     <t>Club les Zéclairs de Nicolet</t>
   </si>
   <si>
@@ -623,7 +614,37 @@
     <t>info@marathonmontmegantic.com</t>
   </si>
   <si>
-    <t>Chem. Roxton S, Roxton Pond, QC J0E 1Z0</t>
+    <t>15 Rue Jacques-Cartier N, Saint-Jean-sur-Richelieu, QC, J3B 8R8</t>
+  </si>
+  <si>
+    <t>1780 Bd David-Bouchard, Roxton Pond, QC J0E 1Z0</t>
+  </si>
+  <si>
+    <t>1380 Rue Montplaisir, Saint-Charles-de-Drummond, QC, J2C 0M6</t>
+  </si>
+  <si>
+    <t>Club Triomax</t>
+  </si>
+  <si>
+    <t>triathlon.qc.ca/</t>
+  </si>
+  <si>
+    <t>Triathlon/Duathlon de St-Lambert</t>
+  </si>
+  <si>
+    <t>430 Rue Riverside, Saint-Lambert, QC J4P 1B6</t>
+  </si>
+  <si>
+    <t>755, rue Cabana, Sherbrooke, QC, J1K 0A6</t>
+  </si>
+  <si>
+    <t>https://www.triathlonsherbrooke.com</t>
+  </si>
+  <si>
+    <t>21 rue des Cèdres, Port-Cartier, QC, G5B 2W5</t>
+  </si>
+  <si>
+    <t>Ville de Port Cartier</t>
   </si>
 </sst>
 </file>
@@ -1091,53 +1112,53 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1161,18 +1182,18 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1184,7 +1205,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1208,18 +1229,18 @@
         <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1241,30 +1262,30 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1276,7 +1297,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1288,30 +1309,30 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1323,7 +1344,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1344,19 +1365,19 @@
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1368,7 +1389,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1389,38 +1410,38 @@
         <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1442,31 +1463,31 @@
         <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1496,31 +1517,31 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1544,34 +1565,34 @@
         <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1589,42 +1610,42 @@
         <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1642,37 +1663,37 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1697,26 +1718,42 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G13" s="1" t="s">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
+      <c r="J13" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
+      <c r="S13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
@@ -1730,34 +1767,38 @@
         <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>131</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -1772,7 +1813,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>30</v>
@@ -1781,22 +1822,40 @@
         <v>23</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="1"/>
+        <v>105</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+      <c r="J15" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
+      <c r="Q15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -1809,7 +1868,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
@@ -1818,27 +1877,34 @@
         <v>31</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
+      <c r="J16" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -1853,7 +1919,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -1890,7 +1956,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>9</v>
@@ -1927,7 +1993,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>13</v>
@@ -1936,10 +2002,10 @@
         <v>33</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="1"/>
@@ -1948,18 +2014,18 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -1974,17 +2040,17 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
@@ -1993,24 +2059,24 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
@@ -2023,17 +2089,17 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -2042,21 +2108,21 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
@@ -2070,17 +2136,17 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="1"/>
@@ -2090,18 +2156,18 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -2115,10 +2181,10 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="4"/>
@@ -2130,13 +2196,13 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -2154,7 +2220,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>11</v>
@@ -2191,16 +2257,16 @@
     </row>
     <row r="25" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -2228,16 +2294,16 @@
     </row>
     <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2265,16 +2331,16 @@
     </row>
     <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2302,14 +2368,14 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -2337,7 +2403,7 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>34</v>
@@ -2351,7 +2417,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -2376,15 +2442,15 @@
     </row>
     <row r="30" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -2393,21 +2459,21 @@
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
       <c r="T30" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="U30" s="9"/>
       <c r="V30" s="9"/>
@@ -2419,7 +2485,7 @@
     </row>
     <row r="31" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>36</v>
@@ -2456,14 +2522,14 @@
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
@@ -2473,18 +2539,18 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
@@ -2499,7 +2565,7 @@
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>39</v>
@@ -2508,7 +2574,7 @@
         <v>22</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2536,21 +2602,21 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2575,7 +2641,7 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>14</v>
@@ -2590,7 +2656,7 @@
       <c r="F35" s="4"/>
       <c r="G35" s="1"/>
       <c r="H35" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -2613,19 +2679,19 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2650,17 +2716,17 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="1"/>
@@ -2669,10 +2735,10 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
@@ -2690,10 +2756,10 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="8"/>
@@ -2722,7 +2788,7 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>40</v>
@@ -2734,22 +2800,22 @@
         <v>41</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F39" s="3"/>
       <c r="L39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>42</v>
@@ -2758,23 +2824,23 @@
         <v>43</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="3"/>
@@ -2785,36 +2851,36 @@
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2854,6 +2920,11 @@
     <hyperlink ref="E11" r:id="rId33" xr:uid="{44C69AEF-33F5-5D43-97CF-FD06227199DB}"/>
     <hyperlink ref="E12" r:id="rId34" xr:uid="{B9A33CB1-2829-2647-947B-C4DAF8119C7B}"/>
     <hyperlink ref="D12" r:id="rId35" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="J13" r:id="rId36" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
+    <hyperlink ref="E13" r:id="rId37" display="https://triathlon.qc.ca/" xr:uid="{8F4832AB-ED93-3945-99FE-21716431AD95}"/>
+    <hyperlink ref="J15" r:id="rId38" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
+    <hyperlink ref="E15" r:id="rId39" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
+    <hyperlink ref="J16" r:id="rId40" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB1DCF3-6346-C44B-900A-2C1DD710F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9335E6A-E7A6-D24A-ADE9-AB74B8B00D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="212">
   <si>
     <t>Événement</t>
   </si>
@@ -203,12 +203,6 @@
     <t>20 juin</t>
   </si>
   <si>
-    <t>20-21 juin</t>
-  </si>
-  <si>
-    <t>27-28 juin</t>
-  </si>
-  <si>
     <t>4 juil.</t>
   </si>
   <si>
@@ -645,6 +639,39 @@
   </si>
   <si>
     <t>Ville de Port Cartier</t>
+  </si>
+  <si>
+    <t>21 juin</t>
+  </si>
+  <si>
+    <t>Ironman 5i50</t>
+  </si>
+  <si>
+    <t>https://www.ironman.com/races/im703-mont-tremblant</t>
+  </si>
+  <si>
+    <t>Ironman</t>
+  </si>
+  <si>
+    <t>https://www.ironman.com/races/5150-mont-tremblant</t>
+  </si>
+  <si>
+    <t>Tremblant5150@theironmangroup.com</t>
+  </si>
+  <si>
+    <t>1000 Chem. des Voyageurs, Mont-Tremblant, QC J8E 1T1</t>
+  </si>
+  <si>
+    <t>https://capquebec.com</t>
+  </si>
+  <si>
+    <t>26-28 juin</t>
+  </si>
+  <si>
+    <t>Quai Saint-André, Québec, QC G1K 3Y2</t>
+  </si>
+  <si>
+    <t>Challenge</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1112,53 +1139,53 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1182,18 +1209,18 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1205,7 +1232,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1229,18 +1256,18 @@
         <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1262,30 +1289,30 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1297,7 +1324,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1309,30 +1336,30 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1344,7 +1371,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1365,19 +1392,19 @@
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1389,7 +1416,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1410,38 +1437,38 @@
         <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1463,31 +1490,31 @@
         <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1517,31 +1544,31 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1565,34 +1592,34 @@
         <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1610,42 +1637,42 @@
         <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1663,37 +1690,37 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1718,41 +1745,41 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -1767,38 +1794,38 @@
         <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -1822,39 +1849,39 @@
         <v>23</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1877,34 +1904,34 @@
         <v>31</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -1919,27 +1946,37 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>55</v>
+        <v>201</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="D17" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
+      <c r="J17" s="2" t="s">
+        <v>207</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
+      <c r="N17" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -1956,28 +1993,38 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>56</v>
+        <v>201</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+      <c r="J18" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
+      <c r="O18" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -1993,40 +2040,46 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>57</v>
+        <v>209</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="K19" s="1"/>
-      <c r="L19" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -2040,17 +2093,19 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="D20" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
@@ -2059,25 +2114,21 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -2089,17 +2140,17 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -2108,23 +2159,25 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="S21" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -2136,38 +2189,40 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F22" s="4"/>
+      <c r="D22" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="M22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -2181,33 +2236,39 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
+      <c r="Q23" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -2220,27 +2281,29 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -2255,55 +2318,55 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2331,16 +2394,16 @@
     </row>
     <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2366,59 +2429,57 @@
       <c r="Z27" s="5"/>
       <c r="AA27" s="5"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+    <row r="28" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="5"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1" t="s">
-        <v>112</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="5"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -2440,155 +2501,157 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+    </row>
+    <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-    </row>
-    <row r="31" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="5" t="s">
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
+    </row>
+    <row r="32" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
-      <c r="V31" s="5"/>
-      <c r="W31" s="5"/>
-      <c r="X31" s="5"/>
-      <c r="Y31" s="5"/>
-      <c r="Z31" s="5"/>
-      <c r="AA31" s="5"/>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
+      <c r="AA32" s="5"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="1"/>
+        <v>94</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="2"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
+      <c r="Q33" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2602,22 +2665,20 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -2641,23 +2702,23 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2" t="s">
-        <v>76</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2676,29 +2737,31 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F36" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="2"/>
+      <c r="H36" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
@@ -2716,30 +2779,27 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="D37" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -2756,22 +2816,30 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="D38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -2788,126 +2856,158 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="L39" t="s">
-        <v>130</v>
-      </c>
-      <c r="M39" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>130</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="F40" s="3"/>
-      <c r="G40" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>115</v>
+      <c r="L40" t="s">
+        <v>128</v>
+      </c>
+      <c r="M40" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="5"/>
+      <c r="G41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>159</v>
+        <v>99</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
-    <hyperlink ref="D30" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
+    <hyperlink ref="D31" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
     <hyperlink ref="D11" r:id="rId3" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D43" r:id="rId4" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D42" r:id="rId5" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D40" r:id="rId6" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D39" r:id="rId7" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D37" r:id="rId8" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D32" r:id="rId9" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D28" r:id="rId10" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
-    <hyperlink ref="D24" r:id="rId11" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D20" r:id="rId12" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
-    <hyperlink ref="D21" r:id="rId13" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D19" r:id="rId14" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D44" r:id="rId4" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D43" r:id="rId5" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D41" r:id="rId6" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D40" r:id="rId7" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D38" r:id="rId8" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D33" r:id="rId9" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D29" r:id="rId10" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
+    <hyperlink ref="D25" r:id="rId11" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D21" r:id="rId12" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
+    <hyperlink ref="D22" r:id="rId13" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D20" r:id="rId14" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
     <hyperlink ref="D16" r:id="rId15" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
     <hyperlink ref="D15" r:id="rId16" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
     <hyperlink ref="D14" r:id="rId17" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
     <hyperlink ref="D13" r:id="rId18" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
     <hyperlink ref="D10" r:id="rId19" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D34" r:id="rId20" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D36" r:id="rId21" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D33" r:id="rId22" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H35" r:id="rId23" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D35" r:id="rId20" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D37" r:id="rId21" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D34" r:id="rId22" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H36" r:id="rId23" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
     <hyperlink ref="D6" r:id="rId24" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
     <hyperlink ref="E2" r:id="rId25" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
     <hyperlink ref="D4" r:id="rId26" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
@@ -2925,6 +3025,8 @@
     <hyperlink ref="J15" r:id="rId38" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
     <hyperlink ref="E15" r:id="rId39" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
     <hyperlink ref="J16" r:id="rId40" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
+    <hyperlink ref="E18" r:id="rId41" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
+    <hyperlink ref="D17" r:id="rId42" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9335E6A-E7A6-D24A-ADE9-AB74B8B00D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DF1946-AA25-5344-8435-B232E1B1FE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -290,9 +290,6 @@
     <t>BIONICK triathlon</t>
   </si>
   <si>
-    <t>Club</t>
-  </si>
-  <si>
     <t>bionicktriathlon.info@gmail.com</t>
   </si>
   <si>
@@ -672,6 +669,9 @@
   </si>
   <si>
     <t>Challenge</t>
+  </si>
+  <si>
+    <t>Organisateur</t>
   </si>
 </sst>
 </file>
@@ -1139,53 +1139,53 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1209,18 +1209,18 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1232,7 +1232,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1256,18 +1256,18 @@
         <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1289,30 +1289,30 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1324,7 +1324,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1336,30 +1336,30 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1371,7 +1371,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1392,19 +1392,19 @@
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1416,7 +1416,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1437,38 +1437,38 @@
         <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1490,31 +1490,31 @@
         <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1544,31 +1544,31 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1592,34 +1592,34 @@
         <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1637,42 +1637,42 @@
         <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1690,37 +1690,37 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1745,41 +1745,41 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -1794,38 +1794,38 @@
         <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -1849,39 +1849,39 @@
         <v>23</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1904,34 +1904,34 @@
         <v>31</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -1946,36 +1946,36 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -2005,25 +2005,25 @@
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
@@ -2052,32 +2052,32 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -2102,10 +2102,10 @@
         <v>33</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
@@ -2114,18 +2114,18 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -2140,17 +2140,17 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1"/>
@@ -2159,24 +2159,24 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
@@ -2189,17 +2189,17 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="1"/>
@@ -2208,21 +2208,21 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -2236,17 +2236,17 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="1"/>
@@ -2256,18 +2256,18 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="4"/>
@@ -2296,13 +2296,13 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -2468,14 +2468,14 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2517,7 +2517,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2542,15 +2542,15 @@
     </row>
     <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
@@ -2559,21 +2559,21 @@
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
       <c r="T31" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U31" s="9"/>
       <c r="V31" s="9"/>
@@ -2625,11 +2625,11 @@
         <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -2639,18 +2639,18 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -2711,7 +2711,7 @@
         <v>82</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2819,14 +2819,14 @@
         <v>71</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="1"/>
@@ -2835,10 +2835,10 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -2859,7 +2859,7 @@
         <v>71</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="8"/>
@@ -2900,17 +2900,17 @@
         <v>41</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="3"/>
       <c r="L40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
@@ -2924,7 +2924,7 @@
         <v>43</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -2932,15 +2932,15 @@
         <v>83</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="3"/>
@@ -2951,36 +2951,36 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DF1946-AA25-5344-8435-B232E1B1FE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D32848-7275-8445-BB44-FBACBE6A8FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D32848-7275-8445-BB44-FBACBE6A8FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561988F5-D7EA-E54B-A6D9-90271150A081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -509,9 +509,6 @@
     <t>TEST</t>
   </si>
   <si>
-    <t>350 Rue Marguerite d'Youville, Nicolet, QC J3T 1X4</t>
-  </si>
-  <si>
     <t>Lieu</t>
   </si>
   <si>
@@ -530,9 +527,6 @@
     <t>GROUPE PENTATHLON</t>
   </si>
   <si>
-    <t>255 Grande Allée O, Québec, QC G1R 2H1</t>
-  </si>
-  <si>
     <t>2500, boulevard de l'Université, Sherbrooke, QC, J1K 2R1</t>
   </si>
   <si>
@@ -563,9 +557,6 @@
     <t>Club de Triathlon de l’Université de Montréal</t>
   </si>
   <si>
-    <t>2300 De la Terrasse St, Québec, Quebec G1V 0A6</t>
-  </si>
-  <si>
     <t>Les Remparts du Collège Militaire Royal de Saint-Jean</t>
   </si>
   <si>
@@ -590,9 +581,6 @@
     <t>Triathlon Laval</t>
   </si>
   <si>
-    <t>1925 Chem. Rouville, Saint-Jean-Baptiste, QC J0L 2B0</t>
-  </si>
-  <si>
     <t>Triathlon Élite Développement</t>
   </si>
   <si>
@@ -608,9 +596,6 @@
     <t>15 Rue Jacques-Cartier N, Saint-Jean-sur-Richelieu, QC, J3B 8R8</t>
   </si>
   <si>
-    <t>1780 Bd David-Bouchard, Roxton Pond, QC J0E 1Z0</t>
-  </si>
-  <si>
     <t>1380 Rue Montplaisir, Saint-Charles-de-Drummond, QC, J2C 0M6</t>
   </si>
   <si>
@@ -623,9 +608,6 @@
     <t>Triathlon/Duathlon de St-Lambert</t>
   </si>
   <si>
-    <t>430 Rue Riverside, Saint-Lambert, QC J4P 1B6</t>
-  </si>
-  <si>
     <t>755, rue Cabana, Sherbrooke, QC, J1K 0A6</t>
   </si>
   <si>
@@ -656,22 +638,40 @@
     <t>Tremblant5150@theironmangroup.com</t>
   </si>
   <si>
-    <t>1000 Chem. des Voyageurs, Mont-Tremblant, QC J8E 1T1</t>
-  </si>
-  <si>
     <t>https://capquebec.com</t>
   </si>
   <si>
     <t>26-28 juin</t>
   </si>
   <si>
-    <t>Quai Saint-André, Québec, QC G1K 3Y2</t>
-  </si>
-  <si>
     <t>Challenge</t>
   </si>
   <si>
     <t>Organisateur</t>
+  </si>
+  <si>
+    <t>1000 Chem. des Voyageurs, Mont-Tremblant, QC, J8E 1T1</t>
+  </si>
+  <si>
+    <t>Quai Saint-André, Québec, QC, G1K 3Y2</t>
+  </si>
+  <si>
+    <t>430 Rue Riverside, Saint-Lambert, QC, J4P 1B6</t>
+  </si>
+  <si>
+    <t>1780 Bd David-Bouchard, Roxton Pond, QC, J0E 1Z0</t>
+  </si>
+  <si>
+    <t>1925 Chem. Rouville, Saint-Jean-Baptiste, QC, J0L 2B0</t>
+  </si>
+  <si>
+    <t>350 Rue Marguerite d'Youville, Nicolet, QC, J3T 1X4</t>
+  </si>
+  <si>
+    <t>255 Grande Allée O, Québec, QC, G1R 2H1</t>
+  </si>
+  <si>
+    <t>2300 De la Terrasse St, Québec, Quebec, G1V 0A6</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1139,7 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>126</v>
@@ -1148,7 +1148,7 @@
         <v>146</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>73</v>
@@ -1157,7 +1157,7 @@
         <v>122</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
@@ -1209,18 +1209,18 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>147</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1256,18 +1256,18 @@
         <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>147</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1292,7 +1292,7 @@
         <v>120</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
@@ -1301,18 +1301,18 @@
         <v>102</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1336,30 +1336,30 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1399,12 +1399,12 @@
         <v>147</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1446,12 +1446,12 @@
         <v>147</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
@@ -1490,7 +1490,7 @@
         <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>142</v>
@@ -1499,12 +1499,12 @@
         <v>147</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
@@ -1550,12 +1550,12 @@
         <v>147</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
@@ -1601,12 +1601,12 @@
         <v>147</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
@@ -1646,18 +1646,18 @@
         <v>118</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
@@ -1696,17 +1696,17 @@
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1748,18 +1748,18 @@
         <v>100</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
@@ -1794,7 +1794,7 @@
         <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
@@ -1812,7 +1812,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
@@ -1852,18 +1852,18 @@
         <v>102</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
@@ -1913,12 +1913,12 @@
         <v>147</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
@@ -1946,30 +1946,30 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -2005,18 +2005,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>147</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
@@ -2052,18 +2052,18 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>147</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561988F5-D7EA-E54B-A6D9-90271150A081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0E4A56-36CB-274F-9C92-1821119CF068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="229">
   <si>
     <t>Événement</t>
   </si>
@@ -356,9 +356,6 @@
     <t>info@triathloncharlevoix.org</t>
   </si>
   <si>
-    <t>info@triathlonpohenegamook.com</t>
-  </si>
-  <si>
     <t xml:space="preserve"> clubtriathlonalma@hotmail.com</t>
   </si>
   <si>
@@ -401,9 +398,6 @@
     <t>15 mars</t>
   </si>
   <si>
-    <t>TRIATHLON VILLE-MARIE</t>
-  </si>
-  <si>
     <t>Distances</t>
   </si>
   <si>
@@ -672,6 +666,63 @@
   </si>
   <si>
     <t>2300 De la Terrasse St, Québec, Quebec, G1V 0A6</t>
+  </si>
+  <si>
+    <t>100 Rue Atawe, Gatineau, QC, J8Y 6V8</t>
+  </si>
+  <si>
+    <t>Club Espoir Triathlon</t>
+  </si>
+  <si>
+    <t>183-D rue Principale, Saint-Aimé-des-Lacs, QC, G0T 1S0‎</t>
+  </si>
+  <si>
+    <t>Triathlon Charlevoix</t>
+  </si>
+  <si>
+    <t>1723 chemin Guérette, Pohénégamook, QC, G0L 1J0</t>
+  </si>
+  <si>
+    <t>MultiAthlon Témiscouata</t>
+  </si>
+  <si>
+    <t>triathlonpohenegamook@gmail.com</t>
+  </si>
+  <si>
+    <t>1385 Chem. de la Marina, Alma, QC, G8B 5W1</t>
+  </si>
+  <si>
+    <t>Club de triathlon Alma</t>
+  </si>
+  <si>
+    <t>Saguenay–Lac-Saint-Jean</t>
+  </si>
+  <si>
+    <t>9, rue Notre-Dame-de-Lourdes, Québec, QC, J9V 1X7</t>
+  </si>
+  <si>
+    <t>Festival des saines habitudes de vie Desjardins</t>
+  </si>
+  <si>
+    <t>info@triathlonvillemarie.com</t>
+  </si>
+  <si>
+    <t>https://www.triathlonvillemarie.com</t>
+  </si>
+  <si>
+    <t>Triathlon de Ville-Marie</t>
+  </si>
+  <si>
+    <t>Abitibi-Témiscamingue</t>
+  </si>
+  <si>
+    <t>Parc de la Baie Magog, Magog, QC, J1X 2B8</t>
+  </si>
+  <si>
+    <t>Club de triathlon Memphrémagog</t>
+  </si>
+  <si>
+    <t>https://trimemphre.com</t>
   </si>
 </sst>
 </file>
@@ -1139,53 +1190,53 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1209,18 +1260,18 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1232,7 +1283,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -1256,18 +1307,18 @@
         <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1289,10 +1340,10 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
@@ -1301,18 +1352,18 @@
         <v>102</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1324,7 +1375,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1336,30 +1387,30 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1371,7 +1422,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1392,19 +1443,19 @@
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1416,7 +1467,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1440,35 +1491,35 @@
         <v>99</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -1490,31 +1541,31 @@
         <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1544,31 +1595,31 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1595,31 +1646,31 @@
         <v>85</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1637,42 +1688,42 @@
         <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1690,37 +1741,37 @@
         <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1748,38 +1799,38 @@
         <v>100</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -1794,7 +1845,7 @@
         <v>52</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
@@ -1803,29 +1854,29 @@
         <v>101</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -1852,36 +1903,36 @@
         <v>102</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1907,31 +1958,31 @@
         <v>103</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -1946,36 +1997,36 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1993,7 +2044,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -2005,25 +2056,25 @@
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -2040,7 +2091,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
@@ -2052,32 +2103,32 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -2105,31 +2156,39 @@
         <v>104</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
+      <c r="T20" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
@@ -2140,45 +2199,55 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="3" t="s">
-        <v>106</v>
+      <c r="C21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="1"/>
+        <v>136</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="T21" s="1"/>
+        <v>125</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
@@ -2194,37 +2263,47 @@
       <c r="B22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="D22" s="3" t="s">
         <v>105</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="S22" s="1"/>
+        <v>125</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -2241,33 +2320,41 @@
       <c r="B23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="1"/>
+      <c r="C23" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="D23" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -2284,29 +2371,43 @@
         <v>87</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="1"/>
+        <v>224</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
+      <c r="Q24" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
@@ -2331,21 +2432,43 @@
       <c r="D25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="1"/>
+      <c r="E25" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
@@ -2475,7 +2598,7 @@
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2517,7 +2640,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2542,15 +2665,15 @@
     </row>
     <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
@@ -2559,21 +2682,21 @@
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
       <c r="T31" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U31" s="9"/>
       <c r="V31" s="9"/>
@@ -2629,7 +2752,7 @@
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -2639,18 +2762,18 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -2823,10 +2946,10 @@
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="1"/>
@@ -2835,10 +2958,10 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -2900,17 +3023,17 @@
         <v>41</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F40" s="3"/>
       <c r="L40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
@@ -2924,7 +3047,7 @@
         <v>43</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -2932,15 +3055,15 @@
         <v>83</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="3"/>
@@ -2951,13 +3074,13 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -2970,17 +3093,17 @@
         <v>98</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2996,37 +3119,38 @@
     <hyperlink ref="D33" r:id="rId9" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
     <hyperlink ref="D29" r:id="rId10" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
     <hyperlink ref="D25" r:id="rId11" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D21" r:id="rId12" xr:uid="{97CF0808-5870-1C48-A3C8-20A09B23DF85}"/>
-    <hyperlink ref="D22" r:id="rId13" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D20" r:id="rId14" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D16" r:id="rId15" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D15" r:id="rId16" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
-    <hyperlink ref="D14" r:id="rId17" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
-    <hyperlink ref="D13" r:id="rId18" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
-    <hyperlink ref="D10" r:id="rId19" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D35" r:id="rId20" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D37" r:id="rId21" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D34" r:id="rId22" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H36" r:id="rId23" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D6" r:id="rId24" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
-    <hyperlink ref="E2" r:id="rId25" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
-    <hyperlink ref="D4" r:id="rId26" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
-    <hyperlink ref="J5" r:id="rId27" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
-    <hyperlink ref="D5" r:id="rId28" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
-    <hyperlink ref="D8" r:id="rId29" display="mailto:triathlondequebec@gmail.com" xr:uid="{73850B34-F1B7-FA48-A070-95C1FFA6FD13}"/>
-    <hyperlink ref="J9" r:id="rId30" display="https://www.google.com/maps/search/?q=Cegep%20R%C3%A9gional%20de%20Lanaudi%C3%A8re%2020%20St-Charles%20Borrom%C3%A9e%20sud%20Joliette%2C%20QC%20J6E%204T1" xr:uid="{B1ADDF14-CFF1-A64F-B451-75A4B753FEB1}"/>
-    <hyperlink ref="J10" r:id="rId31" display="https://www.google.com/maps/search/?q=Centre%20de%20la%20Nature%20%20901%20Avenue%20du%20Parc%20Laval%2C%20QC%20H7E%202T7" xr:uid="{26BECA49-1FB0-6E48-AEA5-586D56437FCE}"/>
-    <hyperlink ref="J11" r:id="rId32" display="https://www.google.com/maps/search/?q=Domaine%20international%20de%20Rouville%201925%20Chem.%20Rouville%2C%20Saint-Jean-Baptiste%2C%20QC%20J0L%202B0%20Saint-Jean-Baptiste%2C%20QC%20" xr:uid="{23DC6288-A0CC-9543-AE7F-D801B3F5045D}"/>
-    <hyperlink ref="E11" r:id="rId33" xr:uid="{44C69AEF-33F5-5D43-97CF-FD06227199DB}"/>
-    <hyperlink ref="E12" r:id="rId34" xr:uid="{B9A33CB1-2829-2647-947B-C4DAF8119C7B}"/>
-    <hyperlink ref="D12" r:id="rId35" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="J13" r:id="rId36" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
-    <hyperlink ref="E13" r:id="rId37" display="https://triathlon.qc.ca/" xr:uid="{8F4832AB-ED93-3945-99FE-21716431AD95}"/>
-    <hyperlink ref="J15" r:id="rId38" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
-    <hyperlink ref="E15" r:id="rId39" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
-    <hyperlink ref="J16" r:id="rId40" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
-    <hyperlink ref="E18" r:id="rId41" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
-    <hyperlink ref="D17" r:id="rId42" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
+    <hyperlink ref="D22" r:id="rId12" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D20" r:id="rId13" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D16" r:id="rId14" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D15" r:id="rId15" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D14" r:id="rId16" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
+    <hyperlink ref="D13" r:id="rId17" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
+    <hyperlink ref="D10" r:id="rId18" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
+    <hyperlink ref="D35" r:id="rId19" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D37" r:id="rId20" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D34" r:id="rId21" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H36" r:id="rId22" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D6" r:id="rId23" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="E2" r:id="rId24" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
+    <hyperlink ref="D4" r:id="rId25" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
+    <hyperlink ref="J5" r:id="rId26" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
+    <hyperlink ref="D5" r:id="rId27" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
+    <hyperlink ref="D8" r:id="rId28" display="mailto:triathlondequebec@gmail.com" xr:uid="{73850B34-F1B7-FA48-A070-95C1FFA6FD13}"/>
+    <hyperlink ref="J9" r:id="rId29" display="https://www.google.com/maps/search/?q=Cegep%20R%C3%A9gional%20de%20Lanaudi%C3%A8re%2020%20St-Charles%20Borrom%C3%A9e%20sud%20Joliette%2C%20QC%20J6E%204T1" xr:uid="{B1ADDF14-CFF1-A64F-B451-75A4B753FEB1}"/>
+    <hyperlink ref="J10" r:id="rId30" display="https://www.google.com/maps/search/?q=Centre%20de%20la%20Nature%20%20901%20Avenue%20du%20Parc%20Laval%2C%20QC%20H7E%202T7" xr:uid="{26BECA49-1FB0-6E48-AEA5-586D56437FCE}"/>
+    <hyperlink ref="J11" r:id="rId31" display="https://www.google.com/maps/search/?q=Domaine%20international%20de%20Rouville%201925%20Chem.%20Rouville%2C%20Saint-Jean-Baptiste%2C%20QC%20J0L%202B0%20Saint-Jean-Baptiste%2C%20QC%20" xr:uid="{23DC6288-A0CC-9543-AE7F-D801B3F5045D}"/>
+    <hyperlink ref="E11" r:id="rId32" xr:uid="{44C69AEF-33F5-5D43-97CF-FD06227199DB}"/>
+    <hyperlink ref="E12" r:id="rId33" xr:uid="{B9A33CB1-2829-2647-947B-C4DAF8119C7B}"/>
+    <hyperlink ref="D12" r:id="rId34" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="J13" r:id="rId35" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
+    <hyperlink ref="E13" r:id="rId36" display="https://triathlon.qc.ca/" xr:uid="{8F4832AB-ED93-3945-99FE-21716431AD95}"/>
+    <hyperlink ref="J15" r:id="rId37" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
+    <hyperlink ref="E15" r:id="rId38" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
+    <hyperlink ref="J16" r:id="rId39" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
+    <hyperlink ref="E18" r:id="rId40" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
+    <hyperlink ref="D17" r:id="rId41" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
+    <hyperlink ref="D21" r:id="rId42" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
+    <hyperlink ref="D24" r:id="rId43" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0E4A56-36CB-274F-9C92-1821119CF068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1F676D-53A5-D746-9194-4C58D30D19C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="245">
   <si>
     <t>Événement</t>
   </si>
@@ -140,24 +140,9 @@
     <t>Outaouais</t>
   </si>
   <si>
-    <t>Tri-O-Lacs Challenge</t>
-  </si>
-  <si>
     <t>info@tri-o-lacs.com</t>
   </si>
   <si>
-    <t>Triathlon de Gaspé</t>
-  </si>
-  <si>
-    <t>Gaspésie</t>
-  </si>
-  <si>
-    <t>info@triathlongaspe.com</t>
-  </si>
-  <si>
-    <t>Triathlon de Verdun</t>
-  </si>
-  <si>
     <t>Triathlon de LaSalle</t>
   </si>
   <si>
@@ -209,42 +194,12 @@
     <t>11-12 juil.</t>
   </si>
   <si>
-    <t>19 juil.</t>
-  </si>
-  <si>
-    <t>Triathlon Victoriaville</t>
-  </si>
-  <si>
-    <t>info@triathlonvictoriaville.com</t>
-  </si>
-  <si>
-    <t>26 juil.</t>
-  </si>
-  <si>
-    <t>Triathlon de la Matapédia</t>
-  </si>
-  <si>
     <t>Bas-Saint-Laurent</t>
   </si>
   <si>
-    <t>Facebook : Triathlon de la Matapédia</t>
-  </si>
-  <si>
-    <t>Juil. (TBC)</t>
-  </si>
-  <si>
-    <t>Triathlon de Portneuf</t>
-  </si>
-  <si>
-    <t>info@triathlonportneuf.com</t>
-  </si>
-  <si>
     <t>2 août</t>
   </si>
   <si>
-    <t>8-9 août</t>
-  </si>
-  <si>
     <t>9 août</t>
   </si>
   <si>
@@ -284,12 +239,6 @@
     <t>Triathlon de Saint-Georges</t>
   </si>
   <si>
-    <t>Beauce</t>
-  </si>
-  <si>
-    <t>BIONICK triathlon</t>
-  </si>
-  <si>
     <t>bionicktriathlon.info@gmail.com</t>
   </si>
   <si>
@@ -320,9 +269,6 @@
     <t>Triathlon du Saguenay</t>
   </si>
   <si>
-    <t>Triathlon au Coeur de la Montérégie (Saint-Césaire)</t>
-  </si>
-  <si>
     <t>Triathlon de Val d'Or</t>
   </si>
   <si>
@@ -359,9 +305,6 @@
     <t xml:space="preserve"> clubtriathlonalma@hotmail.com</t>
   </si>
   <si>
-    <t>support@sportscapitale.com</t>
-  </si>
-  <si>
     <t>Tri-o-lac</t>
   </si>
   <si>
@@ -374,9 +317,6 @@
     <t>Kim Boyd</t>
   </si>
   <si>
-    <t>bionickteam@gmail.com</t>
-  </si>
-  <si>
     <t>triathlon@boucherville.ca</t>
   </si>
   <si>
@@ -404,9 +344,6 @@
     <t>11-13 sept.</t>
   </si>
   <si>
-    <t>Challenge esprit Montréal</t>
-  </si>
-  <si>
     <t>26-27 sept.</t>
   </si>
   <si>
@@ -461,15 +398,6 @@
     <t>https://www.triathlondequebec.com</t>
   </si>
   <si>
-    <t>8 août</t>
-  </si>
-  <si>
-    <t>triosisko.triathlon@gmail.com</t>
-  </si>
-  <si>
-    <t>https://triosiskotriathlon.club/triosisko/triathlon-daiguebelle/</t>
-  </si>
-  <si>
     <t>Affilié Triathlon Québec</t>
   </si>
   <si>
@@ -497,12 +425,6 @@
     <t>Triathlon longue distance</t>
   </si>
   <si>
-    <t>31 octobre</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
     <t>Lieu</t>
   </si>
   <si>
@@ -698,9 +620,6 @@
     <t>Saguenay–Lac-Saint-Jean</t>
   </si>
   <si>
-    <t>9, rue Notre-Dame-de-Lourdes, Québec, QC, J9V 1X7</t>
-  </si>
-  <si>
     <t>Festival des saines habitudes de vie Desjardins</t>
   </si>
   <si>
@@ -710,9 +629,6 @@
     <t>https://www.triathlonvillemarie.com</t>
   </si>
   <si>
-    <t>Triathlon de Ville-Marie</t>
-  </si>
-  <si>
     <t>Abitibi-Témiscamingue</t>
   </si>
   <si>
@@ -723,13 +639,145 @@
   </si>
   <si>
     <t>https://trimemphre.com</t>
+  </si>
+  <si>
+    <t>Triathlon  Ville-Marie</t>
+  </si>
+  <si>
+    <t>9 Rue Notre Dame de Lourdes, Ville-Marie, QC, J9V 1Z8</t>
+  </si>
+  <si>
+    <t>4, rue Louis Jolliet, Sainte-Catherine-de-la-Jacques-Cartier, QC, G3N 2N6</t>
+  </si>
+  <si>
+    <t>Club Capitale Triathlon</t>
+  </si>
+  <si>
+    <t>https://lesclassiquescapitale.com/triathlon-duchesnay-2026-evenement-multisport-nature-pres-de-quebec/#td</t>
+  </si>
+  <si>
+    <t>Défi Tri-O-Lacs</t>
+  </si>
+  <si>
+    <t>https://www.triolacs.com</t>
+  </si>
+  <si>
+    <t>3 Chem. Saint-Emmanuel, Coteau-du-Lac, QC, J0P 1B0</t>
+  </si>
+  <si>
+    <t>2230, rue de la Rivière-aux-Sables, Saguenay, QC, G7X 7W7</t>
+  </si>
+  <si>
+    <t>Club Endurance du fjord</t>
+  </si>
+  <si>
+    <t>https://endurancedufjord.com/endurancefjord/index/triathlon_du_saguenay</t>
+  </si>
+  <si>
+    <t>Triathlon de Verdun Desjardins</t>
+  </si>
+  <si>
+    <t>6500 boulevard Lasalle, Verdun, QC, H4H 2S9</t>
+  </si>
+  <si>
+    <t>https://www.triathlondeverdun.com</t>
+  </si>
+  <si>
+    <t>522 Av. de la Chaudière, Saint-Georges, QC, G5Y 3M8</t>
+  </si>
+  <si>
+    <t>Bionick Triathlon</t>
+  </si>
+  <si>
+    <t>Triathlon Abénaquis</t>
+  </si>
+  <si>
+    <t>18 juil.</t>
+  </si>
+  <si>
+    <t>9 rue des Saules, Sainte-Aurélie, QC, G0M 1M0</t>
+  </si>
+  <si>
+    <t>https://triathlonabenaquis.com</t>
+  </si>
+  <si>
+    <t>triathlonabenaquis@gmail.com</t>
+  </si>
+  <si>
+    <t>240 Rue Victoria, Salaberry-de-Valleyfield, QC, J6T 1B8</t>
+  </si>
+  <si>
+    <t>Triathlon Valleyfield</t>
+  </si>
+  <si>
+    <t>https://triathlonvalleyfield.com</t>
+  </si>
+  <si>
+    <t>109, chemin du Lac Sud, Saint-Mathieu-de-Rioux, QC, G0L 3T0</t>
+  </si>
+  <si>
+    <t>Triathlon au Coeur de la Montérégie</t>
+  </si>
+  <si>
+    <t>1109 Avenue Saint-Paul, Saint-Césaire, QC, J0L 1T0</t>
+  </si>
+  <si>
+    <t>ZJC événements sportifs</t>
+  </si>
+  <si>
+    <t>Rue du Souvenir, Val-d'Or, QC, J9P 0C3</t>
+  </si>
+  <si>
+    <t>goldminer@cablevision.qc.ca</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Triathlondevaldor/</t>
+  </si>
+  <si>
+    <t>7770 Bld LaSalle, LaSalle, QC, H8P 1X6</t>
+  </si>
+  <si>
+    <t>213 1re Avenue, Lac-Etchemin, QC, G0R 1S0</t>
+  </si>
+  <si>
+    <t>https://www.bionicktriathlon.com/triathlonlacetchemin</t>
+  </si>
+  <si>
+    <t>490 Chemin du Lac, Boucherville, QC, J4B 6X3</t>
+  </si>
+  <si>
+    <t>https://www.boucherville.ca/grands-evenements/triathlon-duathlon/</t>
+  </si>
+  <si>
+    <t>Ville de Boucherville</t>
+  </si>
+  <si>
+    <t>Challenge Esprit Montréal</t>
+  </si>
+  <si>
+    <t>https://challenge-espritmontreal.com</t>
+  </si>
+  <si>
+    <t>140 Chem. du Chenal le Moyne, Montréal, QC, H3C 6J6</t>
+  </si>
+  <si>
+    <t>info@challenge-espritmontreal.com</t>
+  </si>
+  <si>
+    <t>40 Chem. du Mont Owls Head, Mansonville, QC, J0E 1X0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Duathlon Long</t>
+  </si>
+  <si>
+    <t>https://www.triathlonepiq.ca</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -742,13 +790,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -766,27 +807,11 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFFC000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFFFC000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFFC000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -796,12 +821,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -817,21 +836,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1167,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1176,10 +1193,10 @@
     <col min="4" max="6" width="37.5" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="16" max="16" width="13.6640625" customWidth="1"/>
-    <col min="18" max="18" width="18.6640625" customWidth="1"/>
+    <col min="18" max="19" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1190,88 +1207,91 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="U1" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB1" s="1"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1282,43 +1302,44 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB2" s="1"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1337,33 +1358,34 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB3" s="1"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1374,43 +1396,44 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB4" s="1"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1421,20 +1444,21 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB5" s="1"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>24</v>
@@ -1443,19 +1467,19 @@
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1466,20 +1490,21 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB6" s="1"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
@@ -1488,40 +1513,40 @@
         <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R7" s="1"/>
-      <c r="S7" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="T7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -1529,43 +1554,44 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="1"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1580,10 +1606,11 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="1"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>2</v>
@@ -1595,31 +1622,31 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1631,10 +1658,11 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="1"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>4</v>
@@ -1643,34 +1671,34 @@
         <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="2" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1682,48 +1710,49 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="1"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1735,43 +1764,44 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="1"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1784,10 +1814,11 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="1"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -1796,87 +1827,88 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R13" s="1"/>
-      <c r="S13" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="S13" s="1"/>
       <c r="T13" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U13" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="1"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -1888,10 +1920,11 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="1"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>30</v>
@@ -1900,39 +1933,39 @@
         <v>23</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1943,10 +1976,11 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="1"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
@@ -1955,34 +1989,34 @@
         <v>31</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -1994,39 +2028,40 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="1"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -2041,10 +2076,11 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="1"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -2056,25 +2092,25 @@
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -2088,47 +2124,48 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="1"/>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -2141,10 +2178,11 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="1"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>13</v>
@@ -2153,158 +2191,160 @@
         <v>33</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="1"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>125</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="S21" s="1"/>
       <c r="T21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U21" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="1"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="T22" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -2312,49 +2352,50 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="1"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -2365,48 +2406,49 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="1"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
@@ -2418,10 +2460,11 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="1"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>11</v>
@@ -2433,43 +2476,43 @@
         <v>12</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="T25" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -2477,178 +2520,241 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
-    </row>
-    <row r="26" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
-      <c r="Z26" s="5"/>
-      <c r="AA26" s="5"/>
-    </row>
-    <row r="27" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="AB25" s="1"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+    </row>
+    <row r="29" spans="1:28" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+      <c r="W29" s="8"/>
+      <c r="X29" s="8"/>
+      <c r="Y29" s="8"/>
+      <c r="Z29" s="8"/>
+      <c r="AA29" s="8"/>
+      <c r="AB29" s="8"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5"/>
-      <c r="Z27" s="5"/>
-      <c r="AA27" s="5"/>
-    </row>
-    <row r="28" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
-      <c r="X28" s="5"/>
-      <c r="Y28" s="5"/>
-      <c r="Z28" s="5"/>
-      <c r="AA28" s="5"/>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="E30" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="G30" s="1" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
+      <c r="L30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
@@ -2662,119 +2768,153 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
-    </row>
-    <row r="31" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-    </row>
-    <row r="32" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="AB30" s="1"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="5"/>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5"/>
-      <c r="Z32" s="5"/>
-      <c r="AA32" s="5"/>
+      <c r="D31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="2"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="J33" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2788,26 +2928,38 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>39</v>
+        <v>226</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+        <v>91</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H34" s="2"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="J34" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -2825,30 +2977,44 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+        <v>197</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>121</v>
+      </c>
       <c r="G35" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="H35" s="2"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>229</v>
+      </c>
       <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
+      <c r="L35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
@@ -2864,293 +3030,246 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="L36" t="s">
+        <v>104</v>
+      </c>
+      <c r="M36" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="D38" s="3" t="s">
-        <v>110</v>
+        <v>241</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
+        <v>239</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="J38" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="L38" s="1" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
+        <v>79</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" t="s">
+        <v>104</v>
+      </c>
+      <c r="N39" t="s">
+        <v>104</v>
+      </c>
+      <c r="O39" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F40" s="3"/>
-      <c r="L40" t="s">
-        <v>125</v>
+        <v>244</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="M40" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O40" t="s">
+        <v>104</v>
       </c>
       <c r="Q40" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="R40" t="s">
+        <v>104</v>
+      </c>
+      <c r="S40" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
-    <hyperlink ref="D31" r:id="rId2" xr:uid="{5D2D8D4D-02CC-ED46-A8B9-DDC82BAF6F9A}"/>
-    <hyperlink ref="D11" r:id="rId3" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D44" r:id="rId4" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D43" r:id="rId5" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D41" r:id="rId6" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D40" r:id="rId7" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D38" r:id="rId8" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D33" r:id="rId9" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D29" r:id="rId10" xr:uid="{F98316FD-1F2F-1C43-9D4F-F226D1C31D47}"/>
-    <hyperlink ref="D25" r:id="rId11" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D22" r:id="rId12" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D20" r:id="rId13" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D16" r:id="rId14" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D15" r:id="rId15" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
-    <hyperlink ref="D14" r:id="rId16" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
-    <hyperlink ref="D13" r:id="rId17" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
-    <hyperlink ref="D10" r:id="rId18" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D35" r:id="rId19" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D37" r:id="rId20" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D34" r:id="rId21" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H36" r:id="rId22" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D6" r:id="rId23" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
-    <hyperlink ref="E2" r:id="rId24" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
-    <hyperlink ref="D4" r:id="rId25" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
-    <hyperlink ref="J5" r:id="rId26" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
-    <hyperlink ref="D5" r:id="rId27" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
-    <hyperlink ref="D8" r:id="rId28" display="mailto:triathlondequebec@gmail.com" xr:uid="{73850B34-F1B7-FA48-A070-95C1FFA6FD13}"/>
-    <hyperlink ref="J9" r:id="rId29" display="https://www.google.com/maps/search/?q=Cegep%20R%C3%A9gional%20de%20Lanaudi%C3%A8re%2020%20St-Charles%20Borrom%C3%A9e%20sud%20Joliette%2C%20QC%20J6E%204T1" xr:uid="{B1ADDF14-CFF1-A64F-B451-75A4B753FEB1}"/>
-    <hyperlink ref="J10" r:id="rId30" display="https://www.google.com/maps/search/?q=Centre%20de%20la%20Nature%20%20901%20Avenue%20du%20Parc%20Laval%2C%20QC%20H7E%202T7" xr:uid="{26BECA49-1FB0-6E48-AEA5-586D56437FCE}"/>
-    <hyperlink ref="J11" r:id="rId31" display="https://www.google.com/maps/search/?q=Domaine%20international%20de%20Rouville%201925%20Chem.%20Rouville%2C%20Saint-Jean-Baptiste%2C%20QC%20J0L%202B0%20Saint-Jean-Baptiste%2C%20QC%20" xr:uid="{23DC6288-A0CC-9543-AE7F-D801B3F5045D}"/>
-    <hyperlink ref="E11" r:id="rId32" xr:uid="{44C69AEF-33F5-5D43-97CF-FD06227199DB}"/>
-    <hyperlink ref="E12" r:id="rId33" xr:uid="{B9A33CB1-2829-2647-947B-C4DAF8119C7B}"/>
-    <hyperlink ref="D12" r:id="rId34" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="J13" r:id="rId35" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
-    <hyperlink ref="E13" r:id="rId36" display="https://triathlon.qc.ca/" xr:uid="{8F4832AB-ED93-3945-99FE-21716431AD95}"/>
-    <hyperlink ref="J15" r:id="rId37" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
-    <hyperlink ref="E15" r:id="rId38" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
-    <hyperlink ref="J16" r:id="rId39" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
-    <hyperlink ref="E18" r:id="rId40" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
-    <hyperlink ref="D17" r:id="rId41" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
-    <hyperlink ref="D21" r:id="rId42" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
-    <hyperlink ref="D24" r:id="rId43" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
+    <hyperlink ref="D11" r:id="rId2" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
+    <hyperlink ref="D40" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D39" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D37" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D36" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D34" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D29" r:id="rId8" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D25" r:id="rId9" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D22" r:id="rId10" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D20" r:id="rId11" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D16" r:id="rId12" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D15" r:id="rId13" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D14" r:id="rId14" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
+    <hyperlink ref="D13" r:id="rId15" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
+    <hyperlink ref="D10" r:id="rId16" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
+    <hyperlink ref="D31" r:id="rId17" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D33" r:id="rId18" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D30" r:id="rId19" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H32" r:id="rId20" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D6" r:id="rId21" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="E2" r:id="rId22" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
+    <hyperlink ref="D4" r:id="rId23" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
+    <hyperlink ref="J5" r:id="rId24" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
+    <hyperlink ref="D5" r:id="rId25" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
+    <hyperlink ref="D8" r:id="rId26" display="mailto:triathlondequebec@gmail.com" xr:uid="{73850B34-F1B7-FA48-A070-95C1FFA6FD13}"/>
+    <hyperlink ref="J9" r:id="rId27" display="https://www.google.com/maps/search/?q=Cegep%20R%C3%A9gional%20de%20Lanaudi%C3%A8re%2020%20St-Charles%20Borrom%C3%A9e%20sud%20Joliette%2C%20QC%20J6E%204T1" xr:uid="{B1ADDF14-CFF1-A64F-B451-75A4B753FEB1}"/>
+    <hyperlink ref="J10" r:id="rId28" display="https://www.google.com/maps/search/?q=Centre%20de%20la%20Nature%20%20901%20Avenue%20du%20Parc%20Laval%2C%20QC%20H7E%202T7" xr:uid="{26BECA49-1FB0-6E48-AEA5-586D56437FCE}"/>
+    <hyperlink ref="J11" r:id="rId29" display="https://www.google.com/maps/search/?q=Domaine%20international%20de%20Rouville%201925%20Chem.%20Rouville%2C%20Saint-Jean-Baptiste%2C%20QC%20J0L%202B0%20Saint-Jean-Baptiste%2C%20QC%20" xr:uid="{23DC6288-A0CC-9543-AE7F-D801B3F5045D}"/>
+    <hyperlink ref="E11" r:id="rId30" xr:uid="{44C69AEF-33F5-5D43-97CF-FD06227199DB}"/>
+    <hyperlink ref="E12" r:id="rId31" xr:uid="{B9A33CB1-2829-2647-947B-C4DAF8119C7B}"/>
+    <hyperlink ref="D12" r:id="rId32" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="J13" r:id="rId33" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
+    <hyperlink ref="E13" r:id="rId34" display="https://triathlon.qc.ca/" xr:uid="{8F4832AB-ED93-3945-99FE-21716431AD95}"/>
+    <hyperlink ref="J15" r:id="rId35" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
+    <hyperlink ref="E15" r:id="rId36" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
+    <hyperlink ref="J16" r:id="rId37" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
+    <hyperlink ref="E18" r:id="rId38" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
+    <hyperlink ref="D17" r:id="rId39" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
+    <hyperlink ref="D21" r:id="rId40" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
+    <hyperlink ref="D24" r:id="rId41" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
+    <hyperlink ref="E27" r:id="rId42" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
+    <hyperlink ref="E28" r:id="rId43" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
+    <hyperlink ref="E29" r:id="rId44" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
+    <hyperlink ref="E30" r:id="rId45" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
+    <hyperlink ref="E26" r:id="rId46" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
+    <hyperlink ref="D26" r:id="rId47" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
+    <hyperlink ref="D35" r:id="rId48" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
+    <hyperlink ref="E39" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
+    <hyperlink ref="E38" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
+    <hyperlink ref="D38" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1F676D-53A5-D746-9194-4C58D30D19C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA37B6EF-A6EF-F941-8E9B-F3B5EA24A669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -467,9 +467,6 @@
     <t>triudem@gmail.com</t>
   </si>
   <si>
-    <t>triathlonudem.com/</t>
-  </si>
-  <si>
     <t>Club de Triathlon de l’Université de Montréal</t>
   </si>
   <si>
@@ -771,6 +768,9 @@
   </si>
   <si>
     <t>https://www.triathlonepiq.ca</t>
+  </si>
+  <si>
+    <t>https://triathlonudem.com</t>
   </si>
 </sst>
 </file>
@@ -838,7 +838,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -847,8 +847,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1216,7 +1214,7 @@
         <v>120</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>58</v>
@@ -1250,7 +1248,7 @@
         <v>127</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>114</v>
@@ -1291,7 +1289,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1339,7 +1337,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1422,13 +1420,13 @@
         <v>142</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1474,12 +1472,12 @@
         <v>121</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1522,12 +1520,12 @@
         <v>121</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
@@ -1567,7 +1565,7 @@
         <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>119</v>
@@ -1581,7 +1579,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
@@ -1628,12 +1626,12 @@
         <v>121</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
@@ -1680,12 +1678,12 @@
         <v>121</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
@@ -1726,18 +1724,18 @@
         <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
@@ -1777,17 +1775,17 @@
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1830,18 +1828,18 @@
         <v>82</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
@@ -1877,7 +1875,7 @@
         <v>47</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
@@ -1895,7 +1893,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
@@ -1936,7 +1934,7 @@
         <v>84</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>121</v>
@@ -1947,7 +1945,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
@@ -1998,12 +1996,12 @@
         <v>121</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
@@ -2032,30 +2030,30 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -2080,7 +2078,7 @@
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -2092,18 +2090,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -2128,7 +2126,7 @@
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
@@ -2140,18 +2138,18 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>121</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -2200,12 +2198,12 @@
         <v>121</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
@@ -2247,7 +2245,7 @@
         <v>52</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>115</v>
@@ -2256,12 +2254,12 @@
         <v>121</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
@@ -2316,12 +2314,12 @@
         <v>121</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
@@ -2362,7 +2360,7 @@
         <v>73</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>88</v>
@@ -2374,12 +2372,12 @@
         <v>121</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -2413,27 +2411,27 @@
         <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>196</v>
-      </c>
       <c r="F24" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
@@ -2476,18 +2474,18 @@
         <v>12</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
@@ -2524,26 +2522,26 @@
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -2576,18 +2574,18 @@
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
@@ -2619,7 +2617,7 @@
         <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>25</v>
@@ -2628,7 +2626,7 @@
         <v>34</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>121</v>
@@ -2639,7 +2637,7 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
@@ -2664,66 +2662,66 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29" spans="1:28" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
-      <c r="W29" s="8"/>
-      <c r="X29" s="8"/>
-      <c r="Y29" s="8"/>
-      <c r="Z29" s="8"/>
-      <c r="AA29" s="8"/>
-      <c r="AB29" s="8"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>22</v>
@@ -2732,18 +2730,18 @@
         <v>60</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
@@ -2788,12 +2786,12 @@
         <v>121</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
@@ -2832,20 +2830,20 @@
         <v>15</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
@@ -2900,7 +2898,7 @@
       <c r="H33" s="2"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
@@ -2931,7 +2929,7 @@
         <v>56</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>23</v>
@@ -2946,12 +2944,12 @@
         <v>121</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
@@ -2983,13 +2981,13 @@
         <v>77</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>121</v>
@@ -3000,7 +2998,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
@@ -3048,7 +3046,7 @@
         <v>121</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L36" t="s">
         <v>104</v>
@@ -3074,19 +3072,19 @@
         <v>67</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>92</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>104</v>
@@ -3100,26 +3098,26 @@
         <v>101</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H38" s="5"/>
       <c r="J38" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>104</v>
@@ -3148,16 +3146,16 @@
         <v>93</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="J39" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>104</v>
@@ -3186,13 +3184,13 @@
         <v>94</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>121</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M40" t="s">
         <v>104</v>
@@ -3270,6 +3268,7 @@
     <hyperlink ref="E39" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
     <hyperlink ref="E38" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
     <hyperlink ref="D38" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
+    <hyperlink ref="E5" r:id="rId52" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA37B6EF-A6EF-F941-8E9B-F3B5EA24A669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57900ACC-72B9-DA4A-B93E-14A94EAFE601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -593,9 +593,6 @@
     <t>Club Espoir Triathlon</t>
   </si>
   <si>
-    <t>183-D rue Principale, Saint-Aimé-des-Lacs, QC, G0T 1S0‎</t>
-  </si>
-  <si>
     <t>Triathlon Charlevoix</t>
   </si>
   <si>
@@ -771,6 +768,9 @@
   </si>
   <si>
     <t>https://triathlonudem.com</t>
+  </si>
+  <si>
+    <t>183 Rue Principale, Saint-Aimé-des-Lacs, QC, G0T 1S0</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1248,7 @@
         <v>127</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>114</v>
@@ -1420,7 +1420,7 @@
         <v>142</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>121</v>
@@ -2245,7 +2245,7 @@
         <v>52</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>115</v>
@@ -2254,12 +2254,12 @@
         <v>121</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
@@ -2314,12 +2314,12 @@
         <v>121</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
@@ -2360,7 +2360,7 @@
         <v>73</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>88</v>
@@ -2372,12 +2372,12 @@
         <v>121</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -2411,27 +2411,27 @@
         <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="F24" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
@@ -2474,18 +2474,18 @@
         <v>12</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
@@ -2522,26 +2522,26 @@
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -2574,18 +2574,18 @@
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
@@ -2617,7 +2617,7 @@
         <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>25</v>
@@ -2626,7 +2626,7 @@
         <v>34</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>121</v>
@@ -2637,7 +2637,7 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
@@ -2670,24 +2670,24 @@
         <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
@@ -2721,7 +2721,7 @@
         <v>54</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>22</v>
@@ -2730,7 +2730,7 @@
         <v>60</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>121</v>
@@ -2741,7 +2741,7 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
@@ -2786,12 +2786,12 @@
         <v>121</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
@@ -2830,20 +2830,20 @@
         <v>15</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>59</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
@@ -2898,7 +2898,7 @@
       <c r="H33" s="2"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
@@ -2929,7 +2929,7 @@
         <v>56</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>23</v>
@@ -2944,12 +2944,12 @@
         <v>121</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
@@ -2981,13 +2981,13 @@
         <v>77</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>121</v>
@@ -2998,7 +2998,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
@@ -3046,7 +3046,7 @@
         <v>121</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L36" t="s">
         <v>104</v>
@@ -3072,19 +3072,19 @@
         <v>67</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>92</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>104</v>
@@ -3098,16 +3098,16 @@
         <v>101</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>121</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="H38" s="5"/>
       <c r="J38" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>104</v>
@@ -3146,16 +3146,16 @@
         <v>93</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="J39" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>104</v>
@@ -3184,13 +3184,13 @@
         <v>94</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>121</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M40" t="s">
         <v>104</v>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57900ACC-72B9-DA4A-B93E-14A94EAFE601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECD2FAE-B547-4247-A944-5D17150B47C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
+    <workbookView xWindow="1020" yWindow="780" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="255">
   <si>
     <t>Événement</t>
   </si>
@@ -771,6 +771,36 @@
   </si>
   <si>
     <t>183 Rue Principale, Saint-Aimé-des-Lacs, QC, G0T 1S0</t>
+  </si>
+  <si>
+    <t>516 Rue Principale, Piopolis, QC, G0Y 1H0</t>
+  </si>
+  <si>
+    <t>22-23 août</t>
+  </si>
+  <si>
+    <t>https://www.triathlonpiopolis.com</t>
+  </si>
+  <si>
+    <t>info@coursesnature.com</t>
+  </si>
+  <si>
+    <t>Triathlon international Piopolis-Carrabassett Valley</t>
+  </si>
+  <si>
+    <t>TriOsisko Triathlon</t>
+  </si>
+  <si>
+    <t>https://triosiskotriathlon.club/triosisko/triathlon-daiguebelle/</t>
+  </si>
+  <si>
+    <t>Triathlon d'Aiguebelle</t>
+  </si>
+  <si>
+    <t>8 août</t>
+  </si>
+  <si>
+    <t>Aiguebelle 14, Taschereau, QC, J0Z 3N0</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AB41"/>
+  <dimension ref="A1:AB43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -2664,30 +2694,28 @@
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>54</v>
+        <v>253</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>208</v>
+        <v>195</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
@@ -2696,9 +2724,7 @@
       <c r="M29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N29" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
@@ -2707,7 +2733,9 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
+      <c r="U29" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
@@ -2721,27 +2749,27 @@
         <v>54</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
@@ -2755,7 +2783,9 @@
       </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
+      <c r="Q30" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
@@ -2770,28 +2800,30 @@
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>66</v>
+        <v>210</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E31" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="F31" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
@@ -2800,7 +2832,9 @@
       <c r="M31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N31" s="1"/>
+      <c r="N31" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -2818,32 +2852,28 @@
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
@@ -2852,53 +2882,50 @@
       <c r="M32" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N32" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-      <c r="Q32" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
@@ -2912,11 +2939,17 @@
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
+      <c r="Q33" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
+      <c r="T33" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
@@ -2926,30 +2959,28 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>226</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="1"/>
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
@@ -2958,7 +2989,9 @@
       <c r="M34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N34" s="1"/>
+      <c r="N34" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -2975,30 +3008,26 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>77</v>
+        <v>249</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
       <c r="H35" s="2"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
@@ -3031,200 +3060,302 @@
         <v>56</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>35</v>
+        <v>224</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>121</v>
       </c>
+      <c r="G36" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="L36" t="s">
-        <v>104</v>
-      </c>
-      <c r="M36" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>104</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F37" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>92</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>231</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="K37" s="1"/>
       <c r="L37" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="M37" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="N37" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="O37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>236</v>
+        <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>239</v>
+        <v>36</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H38" s="5"/>
       <c r="J38" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O38" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="L38" t="s">
+        <v>104</v>
+      </c>
+      <c r="M38" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q38" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="M39" t="s">
-        <v>104</v>
-      </c>
-      <c r="N39" t="s">
-        <v>104</v>
-      </c>
-      <c r="O39" t="s">
+      <c r="N39" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" s="5"/>
+      <c r="J40" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M41" t="s">
+        <v>104</v>
+      </c>
+      <c r="N41" t="s">
+        <v>104</v>
+      </c>
+      <c r="O41" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J40" s="1" t="s">
+      <c r="F42" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="M40" t="s">
-        <v>104</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O40" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>104</v>
-      </c>
-      <c r="R40" t="s">
-        <v>104</v>
-      </c>
-      <c r="S40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
+      <c r="M42" t="s">
+        <v>104</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O42" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>104</v>
+      </c>
+      <c r="R42" t="s">
+        <v>104</v>
+      </c>
+      <c r="S42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
     <hyperlink ref="D11" r:id="rId2" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D40" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D39" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D37" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D36" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D34" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D29" r:id="rId8" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D42" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D41" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D39" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D38" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D36" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D30" r:id="rId8" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
     <hyperlink ref="D25" r:id="rId9" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
     <hyperlink ref="D22" r:id="rId10" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
     <hyperlink ref="D20" r:id="rId11" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
@@ -3233,10 +3364,10 @@
     <hyperlink ref="D14" r:id="rId14" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
     <hyperlink ref="D13" r:id="rId15" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
     <hyperlink ref="D10" r:id="rId16" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D31" r:id="rId17" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D33" r:id="rId18" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D30" r:id="rId19" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H32" r:id="rId20" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D32" r:id="rId17" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D34" r:id="rId18" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D31" r:id="rId19" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H33" r:id="rId20" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
     <hyperlink ref="E2" r:id="rId22" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
     <hyperlink ref="D4" r:id="rId23" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
@@ -3260,15 +3391,18 @@
     <hyperlink ref="D24" r:id="rId41" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
     <hyperlink ref="E27" r:id="rId42" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
     <hyperlink ref="E28" r:id="rId43" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
-    <hyperlink ref="E29" r:id="rId44" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
-    <hyperlink ref="E30" r:id="rId45" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
+    <hyperlink ref="E30" r:id="rId44" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
+    <hyperlink ref="E31" r:id="rId45" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
     <hyperlink ref="E26" r:id="rId46" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
     <hyperlink ref="D26" r:id="rId47" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
-    <hyperlink ref="D35" r:id="rId48" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
-    <hyperlink ref="E39" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
-    <hyperlink ref="E38" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
-    <hyperlink ref="D38" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
+    <hyperlink ref="D37" r:id="rId48" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
+    <hyperlink ref="E41" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
+    <hyperlink ref="E40" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
+    <hyperlink ref="D40" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
     <hyperlink ref="E5" r:id="rId52" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
+    <hyperlink ref="E35" r:id="rId53" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
+    <hyperlink ref="D35" r:id="rId54" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
+    <hyperlink ref="E29" r:id="rId55" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECD2FAE-B547-4247-A944-5D17150B47C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4715C98B-B825-1D4C-A00F-C09893220303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="780" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
+    <workbookView xWindow="1180" yWindow="3460" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4715C98B-B825-1D4C-A00F-C09893220303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3A29C0-8138-C843-858B-F9E550D26331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="3460" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
+    <workbookView xWindow="1180" yWindow="780" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="260">
   <si>
     <t>Événement</t>
   </si>
@@ -801,6 +801,21 @@
   </si>
   <si>
     <t>Aiguebelle 14, Taschereau, QC, J0Z 3N0</t>
+  </si>
+  <si>
+    <t>Triathlon du lac Meech</t>
+  </si>
+  <si>
+    <t>Plage O’Brien, Chelsea, QC, J9B 1H9</t>
+  </si>
+  <si>
+    <t>https://www.somersault.ca/fr/event/meech-lake</t>
+  </si>
+  <si>
+    <t>Adam@Somersault.ca</t>
+  </si>
+  <si>
+    <t>Somersault</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AB43"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -2387,44 +2402,36 @@
         <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>121</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="1" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N23" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -2441,32 +2448,30 @@
         <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="K24" s="1"/>
-      <c r="L24" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
         <v>104</v>
       </c>
@@ -2478,7 +2483,9 @@
       <c r="Q24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="R24" s="1"/>
+      <c r="R24" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -2492,30 +2499,30 @@
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>11</v>
+        <v>199</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F25" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
@@ -2527,20 +2534,14 @@
       <c r="N25" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O25" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="R25" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -2552,37 +2553,55 @@
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>216</v>
+        <v>51</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>215</v>
+        <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>219</v>
+        <v>12</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="1"/>
+        <v>198</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
+      <c r="Q26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
+      <c r="T26" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -2594,42 +2613,34 @@
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>74</v>
+        <v>216</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="E27" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>202</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="K27" s="1"/>
-      <c r="L27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
@@ -2644,30 +2655,28 @@
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>89</v>
+        <v>40</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
@@ -2679,7 +2688,9 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
+      <c r="Q28" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
@@ -2694,28 +2705,30 @@
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>253</v>
+        <v>53</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E29" s="2" t="s">
-        <v>251</v>
+        <v>205</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>121</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>254</v>
+        <v>206</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
@@ -2727,15 +2740,11 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
@@ -2746,30 +2755,28 @@
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>54</v>
+        <v>253</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>208</v>
+        <v>195</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
@@ -2778,9 +2785,7 @@
       <c r="M30" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N30" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
@@ -2789,7 +2794,9 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
+      <c r="U30" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
@@ -2803,27 +2810,27 @@
         <v>54</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
@@ -2837,7 +2844,9 @@
       </c>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
+      <c r="Q31" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
@@ -2852,28 +2861,30 @@
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>66</v>
+        <v>210</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="F32" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
@@ -2882,7 +2893,9 @@
       <c r="M32" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N32" s="1"/>
+      <c r="N32" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
@@ -2898,34 +2911,30 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
@@ -2934,53 +2943,50 @@
       <c r="M33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N33" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="1"/>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
@@ -2994,11 +3000,17 @@
       </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
+      <c r="T34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
@@ -3006,28 +3018,30 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>246</v>
+        <v>61</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>249</v>
+        <v>63</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F35" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="H35" s="2"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
@@ -3039,9 +3053,7 @@
       <c r="N35" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
@@ -3055,32 +3067,28 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>226</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
@@ -3089,8 +3097,12 @@
       <c r="M36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+      <c r="N36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
@@ -3104,32 +3116,32 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1" t="s">
@@ -3138,12 +3150,8 @@
       <c r="M37" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -3157,206 +3165,259 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="F39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L38" t="s">
-        <v>104</v>
-      </c>
-      <c r="M38" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
+      <c r="L39" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="F40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H40" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J40" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+      <c r="L40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="F41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H40" s="5"/>
-      <c r="J40" s="1" t="s">
+      <c r="H41" s="5"/>
+      <c r="J41" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+      <c r="L41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="F42" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J42" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M41" t="s">
-        <v>104</v>
-      </c>
-      <c r="N41" t="s">
-        <v>104</v>
-      </c>
-      <c r="O41" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+      <c r="L42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M42" t="s">
+        <v>104</v>
+      </c>
+      <c r="N42" t="s">
+        <v>104</v>
+      </c>
+      <c r="O42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J42" s="1" t="s">
+      <c r="F43" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="M42" t="s">
-        <v>104</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O42" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>104</v>
-      </c>
-      <c r="R42" t="s">
-        <v>104</v>
-      </c>
-      <c r="S42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
+      <c r="M43" t="s">
+        <v>104</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O43" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>104</v>
+      </c>
+      <c r="R43" t="s">
+        <v>104</v>
+      </c>
+      <c r="S43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
     <hyperlink ref="D11" r:id="rId2" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D42" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D41" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D39" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D38" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D36" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D30" r:id="rId8" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D25" r:id="rId9" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D43" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D42" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D40" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D39" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D37" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D31" r:id="rId8" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D26" r:id="rId9" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
     <hyperlink ref="D22" r:id="rId10" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
     <hyperlink ref="D20" r:id="rId11" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
     <hyperlink ref="D16" r:id="rId12" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
@@ -3364,10 +3425,10 @@
     <hyperlink ref="D14" r:id="rId14" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
     <hyperlink ref="D13" r:id="rId15" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
     <hyperlink ref="D10" r:id="rId16" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D32" r:id="rId17" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D34" r:id="rId18" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D31" r:id="rId19" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H33" r:id="rId20" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D33" r:id="rId17" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D35" r:id="rId18" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D32" r:id="rId19" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H34" r:id="rId20" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
     <hyperlink ref="E2" r:id="rId22" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
     <hyperlink ref="D4" r:id="rId23" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
@@ -3388,21 +3449,23 @@
     <hyperlink ref="E18" r:id="rId38" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
     <hyperlink ref="D17" r:id="rId39" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
     <hyperlink ref="D21" r:id="rId40" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
-    <hyperlink ref="D24" r:id="rId41" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
-    <hyperlink ref="E27" r:id="rId42" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
-    <hyperlink ref="E28" r:id="rId43" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
-    <hyperlink ref="E30" r:id="rId44" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
-    <hyperlink ref="E31" r:id="rId45" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
-    <hyperlink ref="E26" r:id="rId46" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
-    <hyperlink ref="D26" r:id="rId47" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
-    <hyperlink ref="D37" r:id="rId48" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
-    <hyperlink ref="E41" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
-    <hyperlink ref="E40" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
-    <hyperlink ref="D40" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
+    <hyperlink ref="D25" r:id="rId41" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
+    <hyperlink ref="E28" r:id="rId42" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
+    <hyperlink ref="E29" r:id="rId43" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
+    <hyperlink ref="E31" r:id="rId44" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
+    <hyperlink ref="E32" r:id="rId45" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
+    <hyperlink ref="E27" r:id="rId46" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
+    <hyperlink ref="D27" r:id="rId47" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
+    <hyperlink ref="D38" r:id="rId48" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
+    <hyperlink ref="E42" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
+    <hyperlink ref="E41" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
+    <hyperlink ref="D41" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
     <hyperlink ref="E5" r:id="rId52" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
-    <hyperlink ref="E35" r:id="rId53" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
-    <hyperlink ref="D35" r:id="rId54" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
-    <hyperlink ref="E29" r:id="rId55" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
+    <hyperlink ref="E36" r:id="rId53" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
+    <hyperlink ref="D36" r:id="rId54" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
+    <hyperlink ref="E30" r:id="rId55" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
+    <hyperlink ref="E23" r:id="rId56" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
+    <hyperlink ref="D23" r:id="rId57" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3A29C0-8138-C843-858B-F9E550D26331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C8C3BD-F2A2-B748-81EF-88374D6BA477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="780" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="260">
   <si>
     <t>Événement</t>
   </si>
@@ -3396,9 +3396,6 @@
       <c r="Q43" t="s">
         <v>104</v>
       </c>
-      <c r="R43" t="s">
-        <v>104</v>
-      </c>
       <c r="S43" t="s">
         <v>104</v>
       </c>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C8C3BD-F2A2-B748-81EF-88374D6BA477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3EB2EF-7218-B846-80C2-2647EBA655A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="780" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>166</v>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3EB2EF-7218-B846-80C2-2647EBA655A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C19BC75-BC8C-BD48-8BCA-87550FEFFCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="780" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -3278,7 +3278,8 @@
       <c r="J40" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="L40" s="1"/>
+      <c r="M40" s="1" t="s">
         <v>104</v>
       </c>
       <c r="N40" s="1" t="s">

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/mon.projet*(tri)/Web/mon.projet-tri/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C19BC75-BC8C-BD48-8BCA-87550FEFFCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA195E1-66A9-F444-918F-EF5CF714225A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="780" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
+    <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="263">
   <si>
     <t>Événement</t>
   </si>
@@ -816,6 +816,15 @@
   </si>
   <si>
     <t>Somersault</t>
+  </si>
+  <si>
+    <t>531 Rue St Patrick, Thetford Mines, QC, G6G 5W1</t>
+  </si>
+  <si>
+    <t>Triathlon Saint-Noël</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/people/Le-Triathlon-Saint-Noël/61558526142711/</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1970,27 +1979,21 @@
         <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>261</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>84</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>138</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="2" t="s">
-        <v>161</v>
+      <c r="J15" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
@@ -1999,17 +2002,11 @@
       <c r="M15" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -2023,30 +2020,30 @@
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
@@ -2055,13 +2052,17 @@
       <c r="M16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="R16" s="1"/>
+      <c r="R16" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -2078,37 +2079,41 @@
         <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>166</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>170</v>
+        <v>31</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="2" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="L17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
+      <c r="Q17" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -2123,21 +2128,21 @@
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>166</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="D18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -2145,16 +2150,16 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="2" t="s">
         <v>175</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -2171,45 +2176,39 @@
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>171</v>
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>121</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
       <c r="O19" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="P19" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -2225,52 +2224,50 @@
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>121</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="K20" s="1"/>
-      <c r="L20" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
         <v>104</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="O20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
@@ -2281,30 +2278,30 @@
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>188</v>
+        <v>33</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
@@ -2321,13 +2318,9 @@
       <c r="Q21" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="R21" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T21" s="1"/>
       <c r="U21" s="1" t="s">
         <v>104</v>
       </c>
@@ -2341,30 +2334,30 @@
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>87</v>
+        <v>52</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
@@ -2388,7 +2381,9 @@
       <c r="T22" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U22" s="1"/>
+      <c r="U22" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
@@ -2399,41 +2394,53 @@
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>255</v>
+        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>258</v>
+        <v>87</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="G23" s="1" t="s">
-        <v>259</v>
+        <v>185</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="M23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
+      <c r="Q23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
+      <c r="T23" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -2448,44 +2455,36 @@
         <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>121</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="1" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N24" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -2502,32 +2501,30 @@
         <v>70</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="K25" s="1"/>
-      <c r="L25" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
         <v>104</v>
       </c>
@@ -2539,7 +2536,9 @@
       <c r="Q25" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="R25" s="1"/>
+      <c r="R25" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -2553,30 +2552,30 @@
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>11</v>
+        <v>199</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F26" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1" t="s">
@@ -2588,20 +2587,14 @@
       <c r="N26" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="R26" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T26" s="1"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -2613,37 +2606,55 @@
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>216</v>
+        <v>51</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>215</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>219</v>
+        <v>12</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="1"/>
+        <v>198</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
+      <c r="Q27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
+      <c r="T27" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -2655,42 +2666,34 @@
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>216</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="E28" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>202</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="K28" s="1"/>
-      <c r="L28" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
@@ -2705,30 +2708,28 @@
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>89</v>
+        <v>40</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
@@ -2740,7 +2741,9 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
+      <c r="Q29" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
@@ -2755,28 +2758,30 @@
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>253</v>
+        <v>53</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E30" s="2" t="s">
-        <v>251</v>
+        <v>205</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>121</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>254</v>
+        <v>206</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
@@ -2788,15 +2793,11 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
@@ -2807,30 +2808,28 @@
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>54</v>
+        <v>253</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>208</v>
+        <v>195</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
@@ -2839,9 +2838,7 @@
       <c r="M31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N31" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
@@ -2850,7 +2847,9 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
+      <c r="U31" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
@@ -2864,27 +2863,27 @@
         <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
@@ -2898,7 +2897,9 @@
       </c>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
+      <c r="Q32" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
@@ -2913,28 +2914,30 @@
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>66</v>
+        <v>210</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="F33" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
@@ -2943,7 +2946,9 @@
       <c r="M33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
@@ -2961,32 +2966,28 @@
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F34" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
@@ -2995,53 +2996,50 @@
       <c r="M34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N34" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
@@ -3055,11 +3053,17 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
+      <c r="Q35" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
+      <c r="T35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
@@ -3069,26 +3073,28 @@
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>246</v>
+        <v>61</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>249</v>
+        <v>63</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F36" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
@@ -3100,9 +3106,7 @@
       <c r="N36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
@@ -3118,30 +3122,26 @@
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>226</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
       <c r="H37" s="2"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1" t="s">
@@ -3150,8 +3150,12 @@
       <c r="M37" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -3170,27 +3174,27 @@
         <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
@@ -3199,12 +3203,8 @@
       <c r="M38" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N38" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
@@ -3223,210 +3223,263 @@
         <v>56</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>121</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="L39" t="s">
-        <v>104</v>
-      </c>
-      <c r="M39" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>104</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="J40" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N40" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="L40" t="s">
+        <v>104</v>
+      </c>
+      <c r="M40" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q40" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>236</v>
+        <v>37</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>239</v>
+        <v>67</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H41" s="5"/>
+        <v>214</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="J41" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
         <v>104</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O41" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>93</v>
+        <v>239</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>235</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="H42" s="5"/>
       <c r="J42" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="M42" t="s">
-        <v>104</v>
-      </c>
-      <c r="N42" t="s">
-        <v>104</v>
-      </c>
-      <c r="O42" t="s">
+      <c r="M42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43" t="s">
+        <v>104</v>
+      </c>
+      <c r="N43" t="s">
+        <v>104</v>
+      </c>
+      <c r="O43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J43" s="1" t="s">
+      <c r="F44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="M43" t="s">
-        <v>104</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O43" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>104</v>
-      </c>
-      <c r="S43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+      <c r="M44" t="s">
+        <v>104</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>104</v>
+      </c>
+      <c r="S44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
     <hyperlink ref="D11" r:id="rId2" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D43" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D42" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D40" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
-    <hyperlink ref="D39" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
-    <hyperlink ref="D37" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
-    <hyperlink ref="D31" r:id="rId8" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
-    <hyperlink ref="D26" r:id="rId9" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
-    <hyperlink ref="D22" r:id="rId10" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
-    <hyperlink ref="D20" r:id="rId11" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
-    <hyperlink ref="D16" r:id="rId12" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
-    <hyperlink ref="D15" r:id="rId13" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
+    <hyperlink ref="D44" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D43" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D41" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D40" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
+    <hyperlink ref="D38" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
+    <hyperlink ref="D32" r:id="rId8" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
+    <hyperlink ref="D27" r:id="rId9" xr:uid="{E029384D-8BC7-C84B-9B0C-114A7E45599D}"/>
+    <hyperlink ref="D23" r:id="rId10" xr:uid="{F4D8CB89-EDD9-E541-8526-9F767F3234FC}"/>
+    <hyperlink ref="D21" r:id="rId11" xr:uid="{A8C5DFE6-3A20-6B44-AF16-927B12BDE8EF}"/>
+    <hyperlink ref="D17" r:id="rId12" xr:uid="{08CE09B5-E392-3A4A-8651-442EF08BC8BD}"/>
+    <hyperlink ref="D16" r:id="rId13" xr:uid="{F981F615-CF68-9B46-A92A-1BB4C654849A}"/>
     <hyperlink ref="D14" r:id="rId14" xr:uid="{2A7D2B67-AF25-8F42-AB0D-104B326F7391}"/>
     <hyperlink ref="D13" r:id="rId15" xr:uid="{48FC53D1-D940-C34F-9E9A-157647BB920C}"/>
     <hyperlink ref="D10" r:id="rId16" xr:uid="{01D318C7-CE1D-A147-AD73-25E5273474A4}"/>
-    <hyperlink ref="D33" r:id="rId17" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
-    <hyperlink ref="D35" r:id="rId18" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
-    <hyperlink ref="D32" r:id="rId19" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H34" r:id="rId20" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
+    <hyperlink ref="D34" r:id="rId17" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
+    <hyperlink ref="D36" r:id="rId18" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
+    <hyperlink ref="D33" r:id="rId19" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
+    <hyperlink ref="H35" r:id="rId20" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
     <hyperlink ref="D6" r:id="rId21" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
     <hyperlink ref="E2" r:id="rId22" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
     <hyperlink ref="D4" r:id="rId23" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
@@ -3441,29 +3494,30 @@
     <hyperlink ref="D12" r:id="rId32" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
     <hyperlink ref="J13" r:id="rId33" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
     <hyperlink ref="E13" r:id="rId34" display="https://triathlon.qc.ca/" xr:uid="{8F4832AB-ED93-3945-99FE-21716431AD95}"/>
-    <hyperlink ref="J15" r:id="rId35" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
-    <hyperlink ref="E15" r:id="rId36" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
-    <hyperlink ref="J16" r:id="rId37" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
-    <hyperlink ref="E18" r:id="rId38" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
-    <hyperlink ref="D17" r:id="rId39" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
-    <hyperlink ref="D21" r:id="rId40" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
-    <hyperlink ref="D25" r:id="rId41" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
-    <hyperlink ref="E28" r:id="rId42" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
-    <hyperlink ref="E29" r:id="rId43" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
-    <hyperlink ref="E31" r:id="rId44" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
-    <hyperlink ref="E32" r:id="rId45" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
-    <hyperlink ref="E27" r:id="rId46" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
-    <hyperlink ref="D27" r:id="rId47" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
-    <hyperlink ref="D38" r:id="rId48" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
-    <hyperlink ref="E42" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
-    <hyperlink ref="E41" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
-    <hyperlink ref="D41" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
+    <hyperlink ref="J16" r:id="rId35" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
+    <hyperlink ref="E16" r:id="rId36" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
+    <hyperlink ref="J17" r:id="rId37" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
+    <hyperlink ref="E19" r:id="rId38" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
+    <hyperlink ref="D18" r:id="rId39" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
+    <hyperlink ref="D22" r:id="rId40" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
+    <hyperlink ref="D26" r:id="rId41" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
+    <hyperlink ref="E29" r:id="rId42" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
+    <hyperlink ref="E30" r:id="rId43" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
+    <hyperlink ref="E32" r:id="rId44" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
+    <hyperlink ref="E33" r:id="rId45" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
+    <hyperlink ref="E28" r:id="rId46" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
+    <hyperlink ref="D28" r:id="rId47" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
+    <hyperlink ref="D39" r:id="rId48" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
+    <hyperlink ref="E43" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
+    <hyperlink ref="E42" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
+    <hyperlink ref="D42" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
     <hyperlink ref="E5" r:id="rId52" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
-    <hyperlink ref="E36" r:id="rId53" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
-    <hyperlink ref="D36" r:id="rId54" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
-    <hyperlink ref="E30" r:id="rId55" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
-    <hyperlink ref="E23" r:id="rId56" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
-    <hyperlink ref="D23" r:id="rId57" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
+    <hyperlink ref="E37" r:id="rId53" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
+    <hyperlink ref="D37" r:id="rId54" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
+    <hyperlink ref="E31" r:id="rId55" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
+    <hyperlink ref="E24" r:id="rId56" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
+    <hyperlink ref="D24" r:id="rId57" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
+    <hyperlink ref="E15" r:id="rId58" xr:uid="{99B7F71E-AD9D-5B4A-B2B0-5AC88773D33E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA195E1-66A9-F444-918F-EF5CF714225A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB53F8-85A9-DE45-A0CA-FC9F1B529753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -824,7 +824,7 @@
     <t>Triathlon Saint-Noël</t>
   </si>
   <si>
-    <t>https://www.facebook.com/people/Le-Triathlon-Saint-Noël/61558526142711/</t>
+    <t>https://www.facebook.com/profile.php?id=61558526142711</t>
   </si>
 </sst>
 </file>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB53F8-85A9-DE45-A0CA-FC9F1B529753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A976BE-09E2-3C4E-B0CE-ADE2FD7508E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="260">
   <si>
     <t>Événement</t>
   </si>
@@ -212,12 +212,6 @@
     <t>5 sept.</t>
   </si>
   <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>janick.tetreaultmoise@triathlonvalleyfield.com</t>
-  </si>
-  <si>
     <t>info@triathlondeverdun.com</t>
   </si>
   <si>
@@ -314,9 +308,6 @@
     <t>hallemathieu@gmail.com</t>
   </si>
   <si>
-    <t>Kim Boyd</t>
-  </si>
-  <si>
     <t>triathlon@boucherville.ca</t>
   </si>
   <si>
@@ -338,9 +329,6 @@
     <t>15 mars</t>
   </si>
   <si>
-    <t>Distances</t>
-  </si>
-  <si>
     <t>11-13 sept.</t>
   </si>
   <si>
@@ -515,9 +503,6 @@
     <t>Club Triomax</t>
   </si>
   <si>
-    <t>triathlon.qc.ca/</t>
-  </si>
-  <si>
     <t>Triathlon/Duathlon de St-Lambert</t>
   </si>
   <si>
@@ -825,13 +810,19 @@
   </si>
   <si>
     <t>https://www.facebook.com/profile.php?id=61558526142711</t>
+  </si>
+  <si>
+    <t>Piscine</t>
+  </si>
+  <si>
+    <t>https://triathlon.qc.ca</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -852,12 +843,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -892,15 +877,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1236,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:Z45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1244,11 +1228,11 @@
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
     <col min="4" max="6" width="37.5" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" customWidth="1"/>
-    <col min="18" max="19" width="18.6640625" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="16" max="17" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1259,66 +1243,62 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>124</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
@@ -1332,19 +1312,21 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>182</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1353,20 +1335,18 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
+      <c r="S2" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="T2" s="1"/>
-      <c r="U2" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
@@ -1380,19 +1360,21 @@
         <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>181</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1409,36 +1391,36 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
-        <v>135</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1447,46 +1429,46 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
+      <c r="S4" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="T4" s="1"/>
-      <c r="U4" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="2" t="s">
-        <v>141</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1495,20 +1477,18 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
+      <c r="S5" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="T5" s="1"/>
-      <c r="U5" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -1519,20 +1499,20 @@
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H6" s="1"/>
+        <v>140</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1541,20 +1521,18 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
+      <c r="S6" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="T6" s="1"/>
-      <c r="U6" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>43</v>
       </c>
@@ -1565,50 +1543,50 @@
         <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P7" s="1"/>
-      <c r="Q7" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="S7" s="1"/>
-      <c r="T7" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>44</v>
       </c>
@@ -1619,32 +1597,32 @@
         <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H8" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L8" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1657,10 +1635,8 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>45</v>
       </c>
@@ -1674,32 +1650,32 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H9" s="1"/>
+        <v>145</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="I9" s="1"/>
-      <c r="J9" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="J9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P9" s="1"/>
-      <c r="Q9" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1709,10 +1685,8 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
@@ -1723,35 +1697,35 @@
         <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H10" s="1"/>
+        <v>147</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="I10" s="1"/>
-      <c r="J10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="J10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
+      <c r="O10" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P10" s="1"/>
-      <c r="Q10" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1761,51 +1735,49 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H11" s="1"/>
+        <v>148</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>174</v>
+      </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L11" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O11" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P11" s="1"/>
-      <c r="Q11" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1815,46 +1787,44 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>173</v>
+      </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="M12" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -1865,10 +1835,8 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
@@ -1879,89 +1847,91 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="1"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="J14" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
       <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="O14" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -1971,37 +1941,37 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="J15" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
@@ -2015,10 +1985,8 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="1"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
@@ -2029,40 +1997,40 @@
         <v>23</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H16" s="1"/>
+        <v>134</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -2071,10 +2039,8 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>49</v>
       </c>
@@ -2085,35 +2051,35 @@
         <v>31</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H17" s="1"/>
+        <v>159</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="I17" s="1"/>
-      <c r="J17" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="J17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
       <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
+      <c r="O17" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P17" s="1"/>
-      <c r="Q17" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -2123,42 +2089,40 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="M18" s="1"/>
-      <c r="N18" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -2171,12 +2135,10 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -2188,26 +2150,26 @@
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H19" s="1"/>
+        <v>163</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="I19" s="1"/>
-      <c r="J19" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="N19" s="1"/>
-      <c r="O19" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -2219,12 +2181,10 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
@@ -2236,33 +2196,33 @@
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="M20" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -2273,10 +2233,8 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>50</v>
       </c>
@@ -2287,199 +2245,193 @@
         <v>33</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" s="1"/>
+        <v>179</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>178</v>
+      </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="K21" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O21" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P21" s="1"/>
-      <c r="Q21" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
+      <c r="S21" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="T21" s="1"/>
-      <c r="U21" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H22" s="1"/>
+        <v>182</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K22" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="1"/>
       <c r="R22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H23" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="K23" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="1"/>
       <c r="R23" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="S23" s="1"/>
-      <c r="T23" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T23" s="1"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="1"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="H24" s="1"/>
+        <v>254</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="I24" s="1"/>
-      <c r="J24" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="K24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L24" s="1"/>
-      <c r="M24" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -2493,52 +2445,50 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H25" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="I25" s="1"/>
-      <c r="J25" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -2547,51 +2497,49 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K26" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O26" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
@@ -2601,10 +2549,8 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>51</v>
       </c>
@@ -2618,75 +2564,73 @@
         <v>12</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H27" s="1"/>
+        <v>192</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K27" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L27" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N27" s="1"/>
       <c r="O27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="1"/>
       <c r="R27" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="S27" s="1"/>
-      <c r="T27" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="H28" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="I28" s="1"/>
-      <c r="J28" s="1" t="s">
-        <v>217</v>
-      </c>
+      <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -2703,47 +2647,45 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H29" s="1"/>
+        <v>117</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
       <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
+      <c r="O29" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
@@ -2753,15 +2695,13 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>25</v>
@@ -2770,26 +2710,26 @@
         <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H30" s="1"/>
+        <v>87</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
@@ -2803,103 +2743,99 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="H31" s="1"/>
+        <v>245</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>249</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
+      <c r="O31" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P31" s="1"/>
-      <c r="Q31" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
+      <c r="S31" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="T31" s="1"/>
-      <c r="U31" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="H32" s="1"/>
+        <v>186</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="K32" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L32" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O32" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P32" s="1"/>
-      <c r="Q32" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
@@ -2909,46 +2845,44 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H33" s="1"/>
+        <v>148</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="K33" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L33" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
@@ -2961,41 +2895,39 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
-      <c r="AB33" s="1"/>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H34" s="1"/>
+        <v>209</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -3009,10 +2941,8 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -3026,86 +2956,82 @@
         <v>15</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>59</v>
+        <v>216</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K35" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O35" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="2"/>
+      <c r="H36" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="K36" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -3117,45 +3043,43 @@
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="2"/>
+      <c r="H37" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="K37" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L37" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -3166,43 +3090,43 @@
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
+        <v>221</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="J38" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -3215,49 +3139,47 @@
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>121</v>
+        <v>190</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H39" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K39" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="L39" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
@@ -3268,10 +3190,8 @@
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>56</v>
       </c>
@@ -3285,25 +3205,25 @@
         <v>36</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="L40" t="s">
-        <v>104</v>
-      </c>
-      <c r="M40" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J40" t="s">
+        <v>100</v>
+      </c>
+      <c r="K40" t="s">
+        <v>100</v>
+      </c>
+      <c r="O40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>57</v>
       </c>
@@ -3314,147 +3234,146 @@
         <v>38</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="J41" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H42" s="5"/>
+        <v>168</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J42" s="1" t="s">
-        <v>238</v>
+        <v>100</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I43" t="s">
+        <v>100</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
+      </c>
+      <c r="K43" t="s">
+        <v>100</v>
+      </c>
+      <c r="L43" t="s">
+        <v>100</v>
       </c>
       <c r="M43" t="s">
-        <v>104</v>
-      </c>
-      <c r="N43" t="s">
-        <v>104</v>
-      </c>
-      <c r="O43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>240</v>
+        <v>117</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K44" t="s">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="M44" t="s">
-        <v>104</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O44" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="Q44" t="s">
-        <v>104</v>
-      </c>
-      <c r="S44" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
     </row>
@@ -3479,45 +3398,43 @@
     <hyperlink ref="D34" r:id="rId17" xr:uid="{31B70483-26AD-5540-8F40-1AF56BBB959B}"/>
     <hyperlink ref="D36" r:id="rId18" xr:uid="{482C1862-70F5-364D-A72D-E88B0B8ADC21}"/>
     <hyperlink ref="D33" r:id="rId19" xr:uid="{DC6574A2-99BA-0E42-BCBA-8B514C49BD0F}"/>
-    <hyperlink ref="H35" r:id="rId20" xr:uid="{07AF935F-38A6-D34B-807D-21B990C159B1}"/>
-    <hyperlink ref="D6" r:id="rId21" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
-    <hyperlink ref="E2" r:id="rId22" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
-    <hyperlink ref="D4" r:id="rId23" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
-    <hyperlink ref="J5" r:id="rId24" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
-    <hyperlink ref="D5" r:id="rId25" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
-    <hyperlink ref="D8" r:id="rId26" display="mailto:triathlondequebec@gmail.com" xr:uid="{73850B34-F1B7-FA48-A070-95C1FFA6FD13}"/>
-    <hyperlink ref="J9" r:id="rId27" display="https://www.google.com/maps/search/?q=Cegep%20R%C3%A9gional%20de%20Lanaudi%C3%A8re%2020%20St-Charles%20Borrom%C3%A9e%20sud%20Joliette%2C%20QC%20J6E%204T1" xr:uid="{B1ADDF14-CFF1-A64F-B451-75A4B753FEB1}"/>
-    <hyperlink ref="J10" r:id="rId28" display="https://www.google.com/maps/search/?q=Centre%20de%20la%20Nature%20%20901%20Avenue%20du%20Parc%20Laval%2C%20QC%20H7E%202T7" xr:uid="{26BECA49-1FB0-6E48-AEA5-586D56437FCE}"/>
-    <hyperlink ref="J11" r:id="rId29" display="https://www.google.com/maps/search/?q=Domaine%20international%20de%20Rouville%201925%20Chem.%20Rouville%2C%20Saint-Jean-Baptiste%2C%20QC%20J0L%202B0%20Saint-Jean-Baptiste%2C%20QC%20" xr:uid="{23DC6288-A0CC-9543-AE7F-D801B3F5045D}"/>
-    <hyperlink ref="E11" r:id="rId30" xr:uid="{44C69AEF-33F5-5D43-97CF-FD06227199DB}"/>
-    <hyperlink ref="E12" r:id="rId31" xr:uid="{B9A33CB1-2829-2647-947B-C4DAF8119C7B}"/>
-    <hyperlink ref="D12" r:id="rId32" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
-    <hyperlink ref="J13" r:id="rId33" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
-    <hyperlink ref="E13" r:id="rId34" display="https://triathlon.qc.ca/" xr:uid="{8F4832AB-ED93-3945-99FE-21716431AD95}"/>
-    <hyperlink ref="J16" r:id="rId35" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
-    <hyperlink ref="E16" r:id="rId36" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
-    <hyperlink ref="J17" r:id="rId37" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
-    <hyperlink ref="E19" r:id="rId38" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
-    <hyperlink ref="D18" r:id="rId39" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
-    <hyperlink ref="D22" r:id="rId40" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
-    <hyperlink ref="D26" r:id="rId41" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
-    <hyperlink ref="E29" r:id="rId42" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
-    <hyperlink ref="E30" r:id="rId43" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
-    <hyperlink ref="E32" r:id="rId44" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
-    <hyperlink ref="E33" r:id="rId45" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
-    <hyperlink ref="E28" r:id="rId46" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
-    <hyperlink ref="D28" r:id="rId47" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
-    <hyperlink ref="D39" r:id="rId48" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
-    <hyperlink ref="E43" r:id="rId49" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
-    <hyperlink ref="E42" r:id="rId50" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
-    <hyperlink ref="D42" r:id="rId51" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
-    <hyperlink ref="E5" r:id="rId52" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
-    <hyperlink ref="E37" r:id="rId53" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
-    <hyperlink ref="D37" r:id="rId54" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
-    <hyperlink ref="E31" r:id="rId55" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
-    <hyperlink ref="E24" r:id="rId56" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
-    <hyperlink ref="D24" r:id="rId57" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
-    <hyperlink ref="E15" r:id="rId58" xr:uid="{99B7F71E-AD9D-5B4A-B2B0-5AC88773D33E}"/>
+    <hyperlink ref="D6" r:id="rId20" xr:uid="{15316F83-1ABF-2C42-A8BB-415F6B7595F2}"/>
+    <hyperlink ref="E2" r:id="rId21" xr:uid="{F85463A8-57B8-7849-876D-B640B0F40E97}"/>
+    <hyperlink ref="D4" r:id="rId22" display="mailto:info@triathlonsherbrooke.com" xr:uid="{9F2B273E-626F-5D4C-9C0A-069EF242E273}"/>
+    <hyperlink ref="H5" r:id="rId23" display="https://www.google.com/maps/search/?q=CEPSUM%20%202100%20Boulevard%20%C3%89douard-Montpetit%20Montr%C3%A9al%2C%20QC%20H3T%201J4" xr:uid="{17D6AD43-CF01-164F-A417-3889508D5E5F}"/>
+    <hyperlink ref="D5" r:id="rId24" xr:uid="{5354E680-0151-AE47-BE43-C5B48E9F5E4B}"/>
+    <hyperlink ref="D8" r:id="rId25" display="mailto:triathlondequebec@gmail.com" xr:uid="{73850B34-F1B7-FA48-A070-95C1FFA6FD13}"/>
+    <hyperlink ref="H9" r:id="rId26" display="https://www.google.com/maps/search/?q=Cegep%20R%C3%A9gional%20de%20Lanaudi%C3%A8re%2020%20St-Charles%20Borrom%C3%A9e%20sud%20Joliette%2C%20QC%20J6E%204T1" xr:uid="{B1ADDF14-CFF1-A64F-B451-75A4B753FEB1}"/>
+    <hyperlink ref="H10" r:id="rId27" display="https://www.google.com/maps/search/?q=Centre%20de%20la%20Nature%20%20901%20Avenue%20du%20Parc%20Laval%2C%20QC%20H7E%202T7" xr:uid="{26BECA49-1FB0-6E48-AEA5-586D56437FCE}"/>
+    <hyperlink ref="H11" r:id="rId28" display="https://www.google.com/maps/search/?q=Domaine%20international%20de%20Rouville%201925%20Chem.%20Rouville%2C%20Saint-Jean-Baptiste%2C%20QC%20J0L%202B0%20Saint-Jean-Baptiste%2C%20QC%20" xr:uid="{23DC6288-A0CC-9543-AE7F-D801B3F5045D}"/>
+    <hyperlink ref="E11" r:id="rId29" xr:uid="{44C69AEF-33F5-5D43-97CF-FD06227199DB}"/>
+    <hyperlink ref="E12" r:id="rId30" xr:uid="{B9A33CB1-2829-2647-947B-C4DAF8119C7B}"/>
+    <hyperlink ref="D12" r:id="rId31" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
+    <hyperlink ref="H13" r:id="rId32" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
+    <hyperlink ref="H16" r:id="rId33" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
+    <hyperlink ref="E16" r:id="rId34" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
+    <hyperlink ref="H17" r:id="rId35" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
+    <hyperlink ref="E19" r:id="rId36" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
+    <hyperlink ref="D18" r:id="rId37" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
+    <hyperlink ref="D22" r:id="rId38" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
+    <hyperlink ref="D26" r:id="rId39" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
+    <hyperlink ref="E29" r:id="rId40" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
+    <hyperlink ref="E30" r:id="rId41" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
+    <hyperlink ref="E32" r:id="rId42" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
+    <hyperlink ref="E33" r:id="rId43" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
+    <hyperlink ref="E28" r:id="rId44" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
+    <hyperlink ref="D28" r:id="rId45" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
+    <hyperlink ref="D39" r:id="rId46" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
+    <hyperlink ref="E43" r:id="rId47" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
+    <hyperlink ref="E42" r:id="rId48" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
+    <hyperlink ref="D42" r:id="rId49" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
+    <hyperlink ref="E5" r:id="rId50" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
+    <hyperlink ref="E37" r:id="rId51" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
+    <hyperlink ref="D37" r:id="rId52" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
+    <hyperlink ref="E31" r:id="rId53" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
+    <hyperlink ref="E24" r:id="rId54" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
+    <hyperlink ref="D24" r:id="rId55" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
+    <hyperlink ref="E15" r:id="rId56" xr:uid="{99B7F71E-AD9D-5B4A-B2B0-5AC88773D33E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A976BE-09E2-3C4E-B0CE-ADE2FD7508E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515858C2-EC95-E14B-8067-C29979ACF810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="260">
   <si>
     <t>Événement</t>
   </si>
@@ -509,9 +509,6 @@
     <t>755, rue Cabana, Sherbrooke, QC, J1K 0A6</t>
   </si>
   <si>
-    <t>https://www.triathlonsherbrooke.com</t>
-  </si>
-  <si>
     <t>21 rue des Cèdres, Port-Cartier, QC, G5B 2W5</t>
   </si>
   <si>
@@ -816,6 +813,9 @@
   </si>
   <si>
     <t>https://triathlon.qc.ca</t>
+  </si>
+  <si>
+    <t>https://www.triathlonsherbrooke.com/s-triman-2026</t>
   </si>
 </sst>
 </file>
@@ -1252,13 +1252,13 @@
         <v>116</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>118</v>
@@ -1282,7 +1282,7 @@
         <v>123</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>110</v>
@@ -1321,7 +1321,7 @@
         <v>127</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>100</v>
@@ -1369,7 +1369,7 @@
         <v>130</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>100</v>
@@ -1454,7 +1454,7 @@
         <v>138</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>117</v>
@@ -1555,7 +1555,7 @@
         <v>141</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>100</v>
@@ -1759,7 +1759,7 @@
         <v>148</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
@@ -1807,7 +1807,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1850,7 +1850,7 @@
         <v>80</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>117</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>100</v>
@@ -1947,19 +1947,19 @@
         <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>100</v>
@@ -2000,7 +2000,7 @@
         <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>157</v>
+        <v>259</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>117</v>
@@ -2060,12 +2060,14 @@
         <v>117</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I17" s="1"/>
+        <v>157</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="J17" s="1" t="s">
         <v>100</v>
       </c>
@@ -2095,25 +2097,25 @@
         <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2138,7 +2140,7 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -2150,16 +2152,16 @@
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="H19" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2184,7 +2186,7 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
@@ -2196,16 +2198,16 @@
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>117</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2254,10 +2256,10 @@
         <v>117</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
@@ -2299,7 +2301,7 @@
         <v>52</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>111</v>
@@ -2308,10 +2310,10 @@
         <v>117</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
@@ -2366,10 +2368,10 @@
         <v>117</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
@@ -2407,23 +2409,23 @@
         <v>68</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -2454,7 +2456,7 @@
         <v>71</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>86</v>
@@ -2466,10 +2468,10 @@
         <v>117</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -2503,25 +2505,25 @@
         <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
@@ -2564,16 +2566,16 @@
         <v>12</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
@@ -2610,24 +2612,24 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2660,16 +2662,16 @@
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
@@ -2701,7 +2703,7 @@
         <v>53</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>25</v>
@@ -2710,7 +2712,7 @@
         <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>117</v>
@@ -2719,7 +2721,7 @@
         <v>87</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
@@ -2746,26 +2748,26 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>117</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
@@ -2802,22 +2804,22 @@
         <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>88</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>117</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
@@ -2851,7 +2853,7 @@
         <v>54</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>22</v>
@@ -2860,7 +2862,7 @@
         <v>58</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>117</v>
@@ -2869,7 +2871,7 @@
         <v>148</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
@@ -2914,10 +2916,10 @@
         <v>117</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1" t="s">
@@ -2956,16 +2958,16 @@
         <v>15</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>117</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1" t="s">
@@ -3018,7 +3020,7 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1" t="s">
@@ -3046,24 +3048,24 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1" t="s">
@@ -3096,7 +3098,7 @@
         <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>23</v>
@@ -3111,10 +3113,10 @@
         <v>117</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>100</v>
@@ -3148,13 +3150,13 @@
         <v>75</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D39" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>224</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>117</v>
@@ -3163,7 +3165,7 @@
         <v>75</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
@@ -3211,7 +3213,7 @@
         <v>117</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J40" t="s">
         <v>100</v>
@@ -3237,16 +3239,16 @@
         <v>65</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
@@ -3261,25 +3263,25 @@
         <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E42" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>100</v>
@@ -3308,16 +3310,16 @@
         <v>90</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="H43" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I43" t="s">
         <v>100</v>
@@ -3349,13 +3351,13 @@
         <v>91</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>117</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K44" t="s">
         <v>100</v>
@@ -3412,29 +3414,28 @@
     <hyperlink ref="D12" r:id="rId31" xr:uid="{CD9F78C5-7F48-B34A-AF61-AA106AD46820}"/>
     <hyperlink ref="H13" r:id="rId32" display="https://www.google.com/maps/search/?q=R%C3%A9seau%20aquatique%20Drummondville%201380%20Rue%20Montplaisir%20Saint-Charles-de-Drummond%2C%20QC%20J2C%200M6" xr:uid="{C897525A-2634-CD4F-A7DE-7402006DC4A6}"/>
     <hyperlink ref="H16" r:id="rId33" display="https://www.google.com/maps/search/?q=Parc%20Lucien-Blanchard%20755%2C%20rue%20Cabana%20Sherbrooke%2C%20QC%20J1K%200A6" xr:uid="{752DC8E4-D484-F048-9D89-092FE7FBB7C3}"/>
-    <hyperlink ref="E16" r:id="rId34" xr:uid="{D28E3D9E-294E-7E47-A96B-48D8BFD9CFF2}"/>
-    <hyperlink ref="H17" r:id="rId35" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
-    <hyperlink ref="E19" r:id="rId36" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
-    <hyperlink ref="D18" r:id="rId37" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
-    <hyperlink ref="D22" r:id="rId38" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
-    <hyperlink ref="D26" r:id="rId39" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
-    <hyperlink ref="E29" r:id="rId40" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
-    <hyperlink ref="E30" r:id="rId41" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
-    <hyperlink ref="E32" r:id="rId42" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
-    <hyperlink ref="E33" r:id="rId43" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
-    <hyperlink ref="E28" r:id="rId44" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
-    <hyperlink ref="D28" r:id="rId45" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
-    <hyperlink ref="D39" r:id="rId46" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
-    <hyperlink ref="E43" r:id="rId47" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
-    <hyperlink ref="E42" r:id="rId48" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
-    <hyperlink ref="D42" r:id="rId49" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
-    <hyperlink ref="E5" r:id="rId50" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
-    <hyperlink ref="E37" r:id="rId51" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
-    <hyperlink ref="D37" r:id="rId52" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
-    <hyperlink ref="E31" r:id="rId53" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
-    <hyperlink ref="E24" r:id="rId54" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
-    <hyperlink ref="D24" r:id="rId55" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
-    <hyperlink ref="E15" r:id="rId56" xr:uid="{99B7F71E-AD9D-5B4A-B2B0-5AC88773D33E}"/>
+    <hyperlink ref="H17" r:id="rId34" display="https://www.google.com/maps/search/?q=Complexe%20r%C3%A9cr%C3%A9atif%20et%20culturel%2021%20rue%20des%20C%C3%A8dres%20Port-Cartier%2C%20QC%20G5B%202W5" xr:uid="{C869EC4D-382D-D244-A20A-6A081825EF52}"/>
+    <hyperlink ref="E19" r:id="rId35" xr:uid="{41BF8AE3-6775-1E4C-87F9-7A73E606FBC6}"/>
+    <hyperlink ref="D18" r:id="rId36" display="mailto:Tremblant5150@theironmangroup.com" xr:uid="{F15E9485-557A-3A4A-ABE8-F3C1FD09BBE7}"/>
+    <hyperlink ref="D22" r:id="rId37" display="mailto:triathlonpohenegamook@gmail.com" xr:uid="{87E4B1A0-9AF4-404F-853D-9438E64F237E}"/>
+    <hyperlink ref="D26" r:id="rId38" display="mailto:info@triathlonvillemarie.com" xr:uid="{83DF94FE-E7F1-0E45-B255-DDE656E1D5A9}"/>
+    <hyperlink ref="E29" r:id="rId39" location="td" xr:uid="{96CF1F22-FC7F-944E-AD80-49EF18899CE3}"/>
+    <hyperlink ref="E30" r:id="rId40" xr:uid="{09607604-F244-0A4A-912F-3CC98013149E}"/>
+    <hyperlink ref="E32" r:id="rId41" xr:uid="{83AEE81E-B096-3B47-8997-2005FE4CE5BB}"/>
+    <hyperlink ref="E33" r:id="rId42" xr:uid="{70286DAB-B2FF-6C4E-B5B4-A4205F48906E}"/>
+    <hyperlink ref="E28" r:id="rId43" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
+    <hyperlink ref="D28" r:id="rId44" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
+    <hyperlink ref="D39" r:id="rId45" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
+    <hyperlink ref="E43" r:id="rId46" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
+    <hyperlink ref="E42" r:id="rId47" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
+    <hyperlink ref="D42" r:id="rId48" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
+    <hyperlink ref="E5" r:id="rId49" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
+    <hyperlink ref="E37" r:id="rId50" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
+    <hyperlink ref="D37" r:id="rId51" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
+    <hyperlink ref="E31" r:id="rId52" xr:uid="{E71817E8-7F26-B241-BEEE-6D3C52D7EE24}"/>
+    <hyperlink ref="E24" r:id="rId53" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
+    <hyperlink ref="D24" r:id="rId54" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
+    <hyperlink ref="E15" r:id="rId55" xr:uid="{99B7F71E-AD9D-5B4A-B2B0-5AC88773D33E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515858C2-EC95-E14B-8067-C29979ACF810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AD801A-8C11-F741-9967-3802AFBAA241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="264">
   <si>
     <t>Événement</t>
   </si>
@@ -816,6 +816,18 @@
   </si>
   <si>
     <t>https://www.triathlonsherbrooke.com/s-triman-2026</t>
+  </si>
+  <si>
+    <t>12 sept.</t>
+  </si>
+  <si>
+    <t>Triathlon Lac-Poulin</t>
+  </si>
+  <si>
+    <t>https://www.fondationsantebe.com/triathlon-du-lac-poulin-2026</t>
+  </si>
+  <si>
+    <t>165 Rue Vallée, Saint-Benoît-Labre, QC, G0M 1P0</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:Z46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -3260,131 +3272,159 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>233</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>167</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="1"/>
       <c r="H42" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M42" s="1" t="s">
+      <c r="L42" s="1"/>
+      <c r="O42" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>90</v>
+        <v>233</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="I43" t="s">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K43" t="s">
-        <v>100</v>
-      </c>
-      <c r="L43" t="s">
-        <v>100</v>
-      </c>
-      <c r="M43" t="s">
+      <c r="K43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M43" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I44" t="s">
+        <v>100</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K44" t="s">
+        <v>100</v>
+      </c>
+      <c r="L44" t="s">
+        <v>100</v>
+      </c>
+      <c r="M44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H44" s="1" t="s">
+      <c r="F45" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K44" t="s">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M44" t="s">
-        <v>100</v>
-      </c>
-      <c r="O44" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
+      <c r="K45" t="s">
+        <v>100</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M45" t="s">
+        <v>100</v>
+      </c>
+      <c r="O45" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
     <hyperlink ref="D11" r:id="rId2" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D44" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D43" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D45" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D44" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
     <hyperlink ref="D41" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
     <hyperlink ref="D40" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
     <hyperlink ref="D38" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
@@ -3426,9 +3466,9 @@
     <hyperlink ref="E28" r:id="rId43" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
     <hyperlink ref="D28" r:id="rId44" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
     <hyperlink ref="D39" r:id="rId45" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
-    <hyperlink ref="E43" r:id="rId46" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
-    <hyperlink ref="E42" r:id="rId47" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
-    <hyperlink ref="D42" r:id="rId48" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
+    <hyperlink ref="E44" r:id="rId46" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
+    <hyperlink ref="E43" r:id="rId47" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
+    <hyperlink ref="D43" r:id="rId48" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
     <hyperlink ref="E5" r:id="rId49" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
     <hyperlink ref="E37" r:id="rId50" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
     <hyperlink ref="D37" r:id="rId51" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
@@ -3436,6 +3476,7 @@
     <hyperlink ref="E24" r:id="rId53" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
     <hyperlink ref="D24" r:id="rId54" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
     <hyperlink ref="E15" r:id="rId55" xr:uid="{99B7F71E-AD9D-5B4A-B2B0-5AC88773D33E}"/>
+    <hyperlink ref="E42" r:id="rId56" xr:uid="{54A86DC5-3DC3-C148-81FD-78EF570987BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AD801A-8C11-F741-9967-3802AFBAA241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DE1B3C-47DB-1F4D-BABC-F6C4EB3AC91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DE1B3C-47DB-1F4D-BABC-F6C4EB3AC91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3748B21C-B211-7E44-BD8D-0FF9BEA21B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="265">
   <si>
     <t>Événement</t>
   </si>
@@ -828,6 +828,9 @@
   </si>
   <si>
     <t>165 Rue Vallée, Saint-Benoît-Labre, QC, G0M 1P0</t>
+  </si>
+  <si>
+    <t>Club de Triathlon Rive-Sud</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1926,9 @@
       <c r="F14" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>264</v>
+      </c>
       <c r="H14" s="1" t="s">
         <v>171</v>
       </c>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3748B21C-B211-7E44-BD8D-0FF9BEA21B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6A227D-6B86-C849-837A-5301BA1F355D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="265">
   <si>
     <t>Événement</t>
   </si>
@@ -2650,8 +2650,12 @@
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -3482,6 +3486,7 @@
     <hyperlink ref="D24" r:id="rId54" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
     <hyperlink ref="E15" r:id="rId55" xr:uid="{99B7F71E-AD9D-5B4A-B2B0-5AC88773D33E}"/>
     <hyperlink ref="E42" r:id="rId56" xr:uid="{54A86DC5-3DC3-C148-81FD-78EF570987BD}"/>
+    <hyperlink ref="E40" r:id="rId57" xr:uid="{65E3449B-6686-234C-BB38-1415128F216F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10607"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6A227D-6B86-C849-837A-5301BA1F355D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A719D31-D827-7649-B58A-3F13B5CA3EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="265">
   <si>
     <t>Événement</t>
   </si>
@@ -1973,7 +1973,9 @@
       <c r="E15" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
         <v>254</v>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A719D31-D827-7649-B58A-3F13B5CA3EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9EF6F1-B793-7346-91BD-A18C9467279D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="269">
   <si>
     <t>Événement</t>
   </si>
@@ -831,6 +831,18 @@
   </si>
   <si>
     <t>Club de Triathlon Rive-Sud</t>
+  </si>
+  <si>
+    <t>Triathlon de la petite monnaie</t>
+  </si>
+  <si>
+    <t>https://pmonnaie.ca/triathlon-petite-monnaie/</t>
+  </si>
+  <si>
+    <t>COOP solidarité Place du Marché</t>
+  </si>
+  <si>
+    <t>114 Chem. Viceroy, Ripon, QC J0V 1V0</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F99E6A8-617B-A64A-809B-958C9858C33A}">
-  <dimension ref="A1:Z46"/>
+  <dimension ref="A1:Z47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -3250,193 +3262,218 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>37</v>
+        <v>265</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>208</v>
+        <v>266</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" t="s">
+        <v>267</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J41" s="1"/>
+        <v>268</v>
+      </c>
       <c r="K41" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>260</v>
+        <v>57</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="E42" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="1"/>
+        <v>226</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="H42" s="1" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L42" s="1"/>
-      <c r="O42" t="s">
+      <c r="L42" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>233</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>167</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="1"/>
       <c r="H43" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M43" s="1" t="s">
+      <c r="L43" s="1"/>
+      <c r="O43" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>90</v>
+        <v>233</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="I44" t="s">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K44" t="s">
-        <v>100</v>
-      </c>
-      <c r="L44" t="s">
-        <v>100</v>
-      </c>
-      <c r="M44" t="s">
+      <c r="K44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M44" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I45" t="s">
+        <v>100</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K45" t="s">
+        <v>100</v>
+      </c>
+      <c r="L45" t="s">
+        <v>100</v>
+      </c>
+      <c r="M45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="F46" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K45" t="s">
-        <v>100</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M45" t="s">
-        <v>100</v>
-      </c>
-      <c r="O45" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
+      <c r="K46" t="s">
+        <v>100</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M46" t="s">
+        <v>100</v>
+      </c>
+      <c r="O46" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{7DA239F4-B0D6-8743-801E-3E3DC7BE7BA3}"/>
     <hyperlink ref="D11" r:id="rId2" xr:uid="{1551AE21-DFE6-AD44-BE10-AC484F0F242C}"/>
-    <hyperlink ref="D45" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
-    <hyperlink ref="D44" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
-    <hyperlink ref="D41" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
+    <hyperlink ref="D46" r:id="rId3" xr:uid="{C46E322A-EF89-0549-B999-C375F09D13A9}"/>
+    <hyperlink ref="D45" r:id="rId4" xr:uid="{AB7238BF-E0DA-F746-A452-5613A6ED9C82}"/>
+    <hyperlink ref="D42" r:id="rId5" xr:uid="{A537E8BD-0E19-9F4E-8E3C-8BED8814EE2E}"/>
     <hyperlink ref="D40" r:id="rId6" xr:uid="{BD642FE2-17BC-F74D-AFAE-B531E4D3750F}"/>
     <hyperlink ref="D38" r:id="rId7" xr:uid="{CC1F940F-B4CD-8D4A-8FD2-9D5C68424CF2}"/>
     <hyperlink ref="D32" r:id="rId8" display="mailto:endurancefjord@gmail.com" xr:uid="{C7F271DE-962A-0D4F-9B71-A31901AFE67B}"/>
@@ -3477,9 +3514,9 @@
     <hyperlink ref="E28" r:id="rId43" xr:uid="{16EBE685-2775-9240-9A4E-4D175A91AEB9}"/>
     <hyperlink ref="D28" r:id="rId44" xr:uid="{D8325BEF-CBD4-694F-96C7-A466C97BEDC7}"/>
     <hyperlink ref="D39" r:id="rId45" xr:uid="{166DD3CD-131D-7F48-A4D2-A18D46588ADC}"/>
-    <hyperlink ref="E44" r:id="rId46" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
-    <hyperlink ref="E43" r:id="rId47" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
-    <hyperlink ref="D43" r:id="rId48" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
+    <hyperlink ref="E45" r:id="rId46" xr:uid="{7AC4113E-4D0F-FA43-8765-CD14AFD68546}"/>
+    <hyperlink ref="E44" r:id="rId47" xr:uid="{A9528A1D-97BF-0F41-B124-7330849D9627}"/>
+    <hyperlink ref="D44" r:id="rId48" xr:uid="{0736C58A-F44D-D545-B628-12F6A692AC08}"/>
     <hyperlink ref="E5" r:id="rId49" xr:uid="{F195186E-B27D-3F4F-97AE-EEB2BC647C81}"/>
     <hyperlink ref="E37" r:id="rId50" xr:uid="{E5A9A57D-9162-7E49-A980-94D9FB00E89F}"/>
     <hyperlink ref="D37" r:id="rId51" xr:uid="{05ECEADD-64C5-AA48-B5D1-D59C1C765B3C}"/>
@@ -3487,7 +3524,7 @@
     <hyperlink ref="E24" r:id="rId53" xr:uid="{A2EBDD1E-501D-1F4D-94C4-B0DDF2354FC4}"/>
     <hyperlink ref="D24" r:id="rId54" xr:uid="{280FB471-A74A-3049-AD60-840D27077E5F}"/>
     <hyperlink ref="E15" r:id="rId55" xr:uid="{99B7F71E-AD9D-5B4A-B2B0-5AC88773D33E}"/>
-    <hyperlink ref="E42" r:id="rId56" xr:uid="{54A86DC5-3DC3-C148-81FD-78EF570987BD}"/>
+    <hyperlink ref="E43" r:id="rId56" xr:uid="{54A86DC5-3DC3-C148-81FD-78EF570987BD}"/>
     <hyperlink ref="E40" r:id="rId57" xr:uid="{65E3449B-6686-234C-BB38-1415128F216F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Calendrier-2026.xlsx
+++ b/Calendrier-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eire/Library/Mobile Documents/com~apple~CloudDocs/Mon Projet Tri/Web/mon.projet-tri/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9EF6F1-B793-7346-91BD-A18C9467279D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FEBEED-181F-C845-8092-56F249570D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="760" windowWidth="28040" windowHeight="17180" xr2:uid="{336F611A-DD90-FC48-BFF2-43E5ADF4CECF}"/>
   </bookViews>
@@ -842,7 +842,7 @@
     <t>COOP solidarité Place du Marché</t>
   </si>
   <si>
-    <t>114 Chem. Viceroy, Ripon, QC J0V 1V0</t>
+    <t>114 Chem. Viceroy, Ripon, QC, J0V 1V0</t>
   </si>
 </sst>
 </file>
